--- a/output/pdf_financials_xlsx/CLZ.xlsx
+++ b/output/pdf_financials_xlsx/CLZ.xlsx
@@ -1415,10 +1415,10 @@
         </is>
       </c>
       <c r="D16" s="3" t="n">
-        <v>1.234789</v>
+        <v>-1.234789</v>
       </c>
       <c r="E16" s="3" t="n">
-        <v>2.43855</v>
+        <v>-2.43855</v>
       </c>
       <c r="F16" s="1" t="inlineStr">
         <is>
@@ -1453,10 +1453,10 @@
         <v>0.669425</v>
       </c>
       <c r="N16" s="3" t="n">
-        <v>2.22793</v>
+        <v>-2.22793</v>
       </c>
       <c r="O16" s="3" t="n">
-        <v>0.899548</v>
+        <v>-0.899548</v>
       </c>
       <c r="P16" s="3" t="n">
         <v>-0.576283</v>
@@ -1739,10 +1739,10 @@
         </is>
       </c>
       <c r="D20" s="3" t="n">
-        <v>1.234789</v>
+        <v>-1.234789</v>
       </c>
       <c r="E20" s="3" t="n">
-        <v>2.43855</v>
+        <v>-2.43855</v>
       </c>
       <c r="F20" s="1" t="inlineStr">
         <is>
@@ -1777,10 +1777,10 @@
         <v>0.669425</v>
       </c>
       <c r="N20" s="3" t="n">
-        <v>2.22793</v>
+        <v>-2.22793</v>
       </c>
       <c r="O20" s="3" t="n">
-        <v>0.899548</v>
+        <v>-0.899548</v>
       </c>
       <c r="P20" s="3" t="n">
         <v>-0.576283</v>
@@ -1945,10 +1945,10 @@
         <v>-0.367836</v>
       </c>
       <c r="D23" s="3" t="n">
-        <v>1.234789</v>
+        <v>-1.234789</v>
       </c>
       <c r="E23" s="3" t="n">
-        <v>2.43855</v>
+        <v>-2.43855</v>
       </c>
       <c r="F23" s="3" t="n">
         <v>-1.302713</v>
@@ -1975,10 +1975,10 @@
         <v>0.669425</v>
       </c>
       <c r="N23" s="3" t="n">
-        <v>2.22793</v>
+        <v>-2.22793</v>
       </c>
       <c r="O23" s="3" t="n">
-        <v>0.899548</v>
+        <v>-0.899548</v>
       </c>
       <c r="P23" s="3" t="n">
         <v>-0.576283</v>
@@ -2147,10 +2147,10 @@
         </is>
       </c>
       <c r="D26" s="3" t="n">
-        <v>41.159633</v>
+        <v>-41.159633</v>
       </c>
       <c r="E26" s="3" t="n">
-        <v>60.96375</v>
+        <v>-60.96375</v>
       </c>
       <c r="F26" s="1" t="inlineStr">
         <is>
@@ -2185,7 +2185,7 @@
         <v>104.442336</v>
       </c>
       <c r="N26" s="3" t="n">
-        <v>111.3965</v>
+        <v>-111.3965</v>
       </c>
       <c r="O26" s="1" t="inlineStr">
         <is>
@@ -2225,10 +2225,10 @@
         </is>
       </c>
       <c r="D27" s="3" t="n">
-        <v>1.234789</v>
+        <v>-1.234789</v>
       </c>
       <c r="E27" s="3" t="n">
-        <v>2.43855</v>
+        <v>-2.43855</v>
       </c>
       <c r="F27" s="1" t="inlineStr">
         <is>
@@ -2263,10 +2263,10 @@
         <v>0.669425</v>
       </c>
       <c r="N27" s="3" t="n">
-        <v>2.22793</v>
+        <v>-2.22793</v>
       </c>
       <c r="O27" s="3" t="n">
-        <v>0.899548</v>
+        <v>-0.899548</v>
       </c>
       <c r="P27" s="3" t="n">
         <v>-0.576283</v>
@@ -2365,10 +2365,10 @@
         </is>
       </c>
       <c r="D29" s="3" t="n">
-        <v>1.244758</v>
+        <v>-1.22482</v>
       </c>
       <c r="E29" s="3" t="n">
-        <v>2.452399</v>
+        <v>-2.424701</v>
       </c>
       <c r="F29" s="1" t="inlineStr">
         <is>
@@ -2403,10 +2403,10 @@
         <v>0.669425</v>
       </c>
       <c r="N29" s="3" t="n">
-        <v>2.22793</v>
+        <v>-2.22793</v>
       </c>
       <c r="O29" s="3" t="n">
-        <v>0.899548</v>
+        <v>-0.899548</v>
       </c>
       <c r="P29" s="3" t="n">
         <v>-0.5705440000000001</v>
@@ -2527,10 +2527,10 @@
         </is>
       </c>
       <c r="D31" s="3" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="E31" s="3" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="F31" s="1" t="inlineStr">
         <is>
@@ -2565,10 +2565,10 @@
         <v>0</v>
       </c>
       <c r="N31" s="3" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="O31" s="3" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="P31" s="3" t="n">
         <v>-0</v>
@@ -43413,10 +43413,10 @@
         </is>
       </c>
       <c r="G350" s="5" t="n">
-        <v>1.234789</v>
+        <v>-1.234789</v>
       </c>
       <c r="H350" s="5" t="n">
-        <v>2.43855</v>
+        <v>-2.43855</v>
       </c>
       <c r="I350" t="inlineStr">
         <is>
@@ -43459,10 +43459,10 @@
         </is>
       </c>
       <c r="Q350" s="5" t="n">
-        <v>2.22793</v>
+        <v>-2.22793</v>
       </c>
       <c r="R350" s="5" t="n">
-        <v>0.899548</v>
+        <v>-0.899548</v>
       </c>
       <c r="S350" t="inlineStr">
         <is>
@@ -48182,7 +48182,7 @@
         </is>
       </c>
       <c r="G397" s="5" t="n">
-        <v>0.367836</v>
+        <v>-0.367836</v>
       </c>
       <c r="H397" t="inlineStr">
         <is>

--- a/output/pdf_financials_xlsx/CLZ.xlsx
+++ b/output/pdf_financials_xlsx/CLZ.xlsx
@@ -1151,10 +1151,10 @@
         </is>
       </c>
       <c r="H12" s="3" t="n">
-        <v>0</v>
+        <v>-0.013039</v>
       </c>
       <c r="I12" s="3" t="n">
-        <v>0</v>
+        <v>-0.010588</v>
       </c>
       <c r="J12" s="1" t="inlineStr">
         <is>
@@ -1167,16 +1167,16 @@
         </is>
       </c>
       <c r="L12" s="3" t="n">
-        <v>0</v>
+        <v>-0.000934</v>
       </c>
       <c r="M12" s="3" t="n">
-        <v>0</v>
+        <v>-0.01165</v>
       </c>
       <c r="N12" s="3" t="n">
-        <v>0</v>
+        <v>-0.002467</v>
       </c>
       <c r="O12" s="3" t="n">
-        <v>0</v>
+        <v>-0.001684</v>
       </c>
       <c r="P12" s="3" t="n">
         <v>0</v>
@@ -2241,10 +2241,10 @@
         </is>
       </c>
       <c r="H27" s="3" t="n">
-        <v>-3.577456</v>
+        <v>-3.564417</v>
       </c>
       <c r="I27" s="3" t="n">
-        <v>-1.640993</v>
+        <v>-1.630405</v>
       </c>
       <c r="J27" s="1" t="inlineStr">
         <is>
@@ -2257,16 +2257,16 @@
         </is>
       </c>
       <c r="L27" s="3" t="n">
-        <v>-1.443666</v>
+        <v>-1.442732</v>
       </c>
       <c r="M27" s="3" t="n">
-        <v>0.669425</v>
+        <v>0.681075</v>
       </c>
       <c r="N27" s="3" t="n">
-        <v>-2.22793</v>
+        <v>-2.225463</v>
       </c>
       <c r="O27" s="3" t="n">
-        <v>-0.899548</v>
+        <v>-0.897864</v>
       </c>
       <c r="P27" s="3" t="n">
         <v>-0.576283</v>
@@ -2381,10 +2381,10 @@
         </is>
       </c>
       <c r="H29" s="3" t="n">
-        <v>-3.568656</v>
+        <v>-3.555617</v>
       </c>
       <c r="I29" s="3" t="n">
-        <v>-1.634183</v>
+        <v>-1.623595</v>
       </c>
       <c r="J29" s="1" t="inlineStr">
         <is>
@@ -2397,16 +2397,16 @@
         </is>
       </c>
       <c r="L29" s="3" t="n">
-        <v>-1.439968</v>
+        <v>-1.439034</v>
       </c>
       <c r="M29" s="3" t="n">
-        <v>0.669425</v>
+        <v>0.681075</v>
       </c>
       <c r="N29" s="3" t="n">
-        <v>-2.22793</v>
+        <v>-2.225463</v>
       </c>
       <c r="O29" s="3" t="n">
-        <v>-0.899548</v>
+        <v>-0.897864</v>
       </c>
       <c r="P29" s="3" t="n">
         <v>-0.5705440000000001</v>
@@ -2686,10 +2686,10 @@
         </is>
       </c>
       <c r="B34" s="3" t="n">
-        <v>0</v>
+        <v>0.008266000000000001</v>
       </c>
       <c r="C34" s="3" t="n">
-        <v>0</v>
+        <v>0.080063</v>
       </c>
       <c r="D34" s="3" t="n">
         <v>0.080063</v>
@@ -2701,10 +2701,10 @@
         <v>0.7726</v>
       </c>
       <c r="G34" s="3" t="n">
-        <v>0</v>
+        <v>0.119692</v>
       </c>
       <c r="H34" s="3" t="n">
-        <v>0</v>
+        <v>0.125226</v>
       </c>
       <c r="I34" s="3" t="n">
         <v>0.203294</v>
@@ -2722,19 +2722,19 @@
         <v>0.818015</v>
       </c>
       <c r="N34" s="3" t="n">
-        <v>0</v>
+        <v>0.451241</v>
       </c>
       <c r="O34" s="3" t="n">
-        <v>0</v>
+        <v>0.054272</v>
       </c>
       <c r="P34" s="3" t="n">
-        <v>0</v>
+        <v>0.006952</v>
       </c>
       <c r="Q34" s="3" t="n">
-        <v>0</v>
+        <v>0.004865</v>
       </c>
       <c r="R34" s="3" t="n">
-        <v>0</v>
+        <v>0.031857</v>
       </c>
     </row>
     <row r="35">
@@ -2802,10 +2802,10 @@
         </is>
       </c>
       <c r="B36" s="3" t="n">
-        <v>0</v>
+        <v>0.008266000000000001</v>
       </c>
       <c r="C36" s="3" t="n">
-        <v>0</v>
+        <v>0.080063</v>
       </c>
       <c r="D36" s="3" t="n">
         <v>0.080063</v>
@@ -2817,10 +2817,10 @@
         <v>0.7726</v>
       </c>
       <c r="G36" s="3" t="n">
-        <v>0</v>
+        <v>0.119692</v>
       </c>
       <c r="H36" s="3" t="n">
-        <v>0</v>
+        <v>0.125226</v>
       </c>
       <c r="I36" s="3" t="n">
         <v>0.574294</v>
@@ -2838,19 +2838,19 @@
         <v>0.818015</v>
       </c>
       <c r="N36" s="3" t="n">
-        <v>0</v>
+        <v>0.451241</v>
       </c>
       <c r="O36" s="3" t="n">
-        <v>0</v>
+        <v>0.054272</v>
       </c>
       <c r="P36" s="3" t="n">
-        <v>0</v>
+        <v>0.006952</v>
       </c>
       <c r="Q36" s="3" t="n">
-        <v>0</v>
+        <v>0.004865</v>
       </c>
       <c r="R36" s="3" t="n">
-        <v>0</v>
+        <v>0.031857</v>
       </c>
     </row>
     <row r="37">
@@ -3543,10 +3543,10 @@
         <v>0</v>
       </c>
       <c r="Q48" s="3" t="n">
-        <v>0.009428000000000001</v>
+        <v>0.004563</v>
       </c>
       <c r="R48" s="3" t="n">
-        <v>0.032056</v>
+        <v>0.000199</v>
       </c>
     </row>
     <row r="49">
@@ -9059,7 +9059,7 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>Cash</t>
+          <t>CashAndCashEquivalents</t>
         </is>
       </c>
       <c r="E2" s="5" t="n">
@@ -18586,7 +18586,7 @@
       </c>
       <c r="D99" t="inlineStr">
         <is>
-          <t>Cash</t>
+          <t>CashAndCashEquivalents</t>
         </is>
       </c>
       <c r="E99" t="inlineStr">
@@ -19901,7 +19901,7 @@
       </c>
       <c r="D112" t="inlineStr">
         <is>
-          <t>Cash</t>
+          <t>CashAndCashEquivalents</t>
         </is>
       </c>
       <c r="E112" t="inlineStr">
@@ -42629,7 +42629,7 @@
       </c>
       <c r="D342" t="inlineStr">
         <is>
-          <t>InterestIncome</t>
+          <t>InterestIncomeNonOperating</t>
         </is>
       </c>
       <c r="E342" t="inlineStr">

--- a/output/pdf_financials_xlsx/CLZ.xlsx
+++ b/output/pdf_financials_xlsx/CLZ.xlsx
@@ -564,15 +564,11 @@
           <t>Revenue</t>
         </is>
       </c>
-      <c r="B4" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="C4" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="B4" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="C4" s="3" t="n">
+        <v>0</v>
       </c>
       <c r="D4" s="3" t="n">
         <v>0</v>
@@ -580,15 +576,11 @@
       <c r="E4" s="3" t="n">
         <v>0</v>
       </c>
-      <c r="F4" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="G4" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="F4" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="G4" s="3" t="n">
+        <v>0</v>
       </c>
       <c r="H4" s="3" t="n">
         <v>0</v>
@@ -596,15 +588,11 @@
       <c r="I4" s="3" t="n">
         <v>0</v>
       </c>
-      <c r="J4" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="K4" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="J4" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="K4" s="3" t="n">
+        <v>0</v>
       </c>
       <c r="L4" s="3" t="n">
         <v>0</v>
@@ -634,15 +622,11 @@
           <t xml:space="preserve">  Cost of Goods Sold</t>
         </is>
       </c>
-      <c r="B5" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="C5" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="B5" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="C5" s="3" t="n">
+        <v>0</v>
       </c>
       <c r="D5" s="3" t="n">
         <v>0</v>
@@ -650,15 +634,11 @@
       <c r="E5" s="3" t="n">
         <v>0</v>
       </c>
-      <c r="F5" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="G5" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="F5" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="G5" s="3" t="n">
+        <v>0</v>
       </c>
       <c r="H5" s="3" t="n">
         <v>0</v>
@@ -666,15 +646,11 @@
       <c r="I5" s="3" t="n">
         <v>0</v>
       </c>
-      <c r="J5" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="K5" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="J5" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="K5" s="3" t="n">
+        <v>0</v>
       </c>
       <c r="L5" s="3" t="n">
         <v>0</v>
@@ -704,15 +680,11 @@
           <t>Gross Profit</t>
         </is>
       </c>
-      <c r="B6" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="C6" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="B6" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="C6" s="3" t="n">
+        <v>0</v>
       </c>
       <c r="D6" s="3" t="n">
         <v>0</v>
@@ -720,15 +692,11 @@
       <c r="E6" s="3" t="n">
         <v>0</v>
       </c>
-      <c r="F6" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="G6" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="F6" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="G6" s="3" t="n">
+        <v>0</v>
       </c>
       <c r="H6" s="3" t="n">
         <v>0</v>
@@ -736,15 +704,11 @@
       <c r="I6" s="3" t="n">
         <v>0</v>
       </c>
-      <c r="J6" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="K6" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="J6" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="K6" s="3" t="n">
+        <v>0</v>
       </c>
       <c r="L6" s="3" t="n">
         <v>0</v>
@@ -774,31 +738,23 @@
           <t xml:space="preserve">  Selling, General, &amp; Admin. Expense</t>
         </is>
       </c>
-      <c r="B7" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="C7" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="B7" s="3" t="n">
+        <v>0.19265</v>
+      </c>
+      <c r="C7" s="3" t="n">
+        <v>0.175396</v>
       </c>
       <c r="D7" s="3" t="n">
-        <v>0.156659</v>
+        <v>0.196659</v>
       </c>
       <c r="E7" s="3" t="n">
-        <v>0.219103</v>
-      </c>
-      <c r="F7" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="G7" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+        <v>0.259103</v>
+      </c>
+      <c r="F7" s="3" t="n">
+        <v>0.104798</v>
+      </c>
+      <c r="G7" s="3" t="n">
+        <v>0.089855</v>
       </c>
       <c r="H7" s="3" t="n">
         <v>0.08529200000000001</v>
@@ -806,27 +762,23 @@
       <c r="I7" s="3" t="n">
         <v>0.088116</v>
       </c>
-      <c r="J7" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="K7" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="J7" s="3" t="n">
+        <v>0.23206</v>
+      </c>
+      <c r="K7" s="3" t="n">
+        <v>0.309489</v>
       </c>
       <c r="L7" s="3" t="n">
-        <v>0.199036</v>
+        <v>0.241036</v>
       </c>
       <c r="M7" s="3" t="n">
-        <v>0.195742</v>
+        <v>0.231742</v>
       </c>
       <c r="N7" s="3" t="n">
-        <v>0.134159</v>
+        <v>0.170159</v>
       </c>
       <c r="O7" s="3" t="n">
-        <v>0.132591</v>
+        <v>0.141591</v>
       </c>
       <c r="P7" s="3" t="n">
         <v>0.110874</v>
@@ -844,15 +796,11 @@
           <t xml:space="preserve">  Research &amp; Development</t>
         </is>
       </c>
-      <c r="B8" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="C8" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="B8" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="C8" s="3" t="n">
+        <v>0</v>
       </c>
       <c r="D8" s="3" t="n">
         <v>0</v>
@@ -860,15 +808,11 @@
       <c r="E8" s="3" t="n">
         <v>0</v>
       </c>
-      <c r="F8" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="G8" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="F8" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="G8" s="3" t="n">
+        <v>0</v>
       </c>
       <c r="H8" s="3" t="n">
         <v>0</v>
@@ -876,15 +820,11 @@
       <c r="I8" s="3" t="n">
         <v>0</v>
       </c>
-      <c r="J8" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="K8" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="J8" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="K8" s="3" t="n">
+        <v>0</v>
       </c>
       <c r="L8" s="3" t="n">
         <v>0</v>
@@ -914,15 +854,11 @@
           <t xml:space="preserve">  Other Operating Expense</t>
         </is>
       </c>
-      <c r="B9" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="C9" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="B9" s="3" t="n">
+        <v>0.014412</v>
+      </c>
+      <c r="C9" s="3" t="n">
+        <v>0.01169</v>
       </c>
       <c r="D9" s="3" t="n">
         <v>0.008487</v>
@@ -930,15 +866,11 @@
       <c r="E9" s="3" t="n">
         <v>0.03145</v>
       </c>
-      <c r="F9" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="G9" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="F9" s="3" t="n">
+        <v>0.02669</v>
+      </c>
+      <c r="G9" s="3" t="n">
+        <v>0.013153</v>
       </c>
       <c r="H9" s="3" t="n">
         <v>0.01069</v>
@@ -946,15 +878,11 @@
       <c r="I9" s="3" t="n">
         <v>0.007879000000000001</v>
       </c>
-      <c r="J9" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="K9" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="J9" s="3" t="n">
+        <v>0.020092</v>
+      </c>
+      <c r="K9" s="3" t="n">
+        <v>0.025084</v>
       </c>
       <c r="L9" s="3" t="n">
         <v>0.011401</v>
@@ -984,47 +912,35 @@
           <t xml:space="preserve">  Total Operating Expense</t>
         </is>
       </c>
-      <c r="B10" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="C10" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="B10" s="3" t="n">
+        <v>0.207062</v>
+      </c>
+      <c r="C10" s="3" t="n">
+        <v>0.187086</v>
       </c>
       <c r="D10" s="3" t="n">
-        <v>0.165146</v>
+        <v>0.205146</v>
       </c>
       <c r="E10" s="3" t="n">
-        <v>0.250553</v>
-      </c>
-      <c r="F10" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="G10" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+        <v>0.290553</v>
+      </c>
+      <c r="F10" s="3" t="n">
+        <v>1.302713</v>
+      </c>
+      <c r="G10" s="3" t="n">
+        <v>1.356318</v>
       </c>
       <c r="H10" s="3" t="n">
-        <v>0.095982</v>
+        <v>3.577456</v>
       </c>
       <c r="I10" s="3" t="n">
-        <v>0.095995</v>
-      </c>
-      <c r="J10" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="K10" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+        <v>1.640993</v>
+      </c>
+      <c r="J10" s="3" t="n">
+        <v>1.584424</v>
+      </c>
+      <c r="K10" s="3" t="n">
+        <v>2.254398</v>
       </c>
       <c r="L10" s="3" t="n">
         <v>1.427664</v>
@@ -1054,47 +970,35 @@
           <t>Operating Income</t>
         </is>
       </c>
-      <c r="B11" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="C11" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="B11" s="3" t="n">
+        <v>0.7201</v>
+      </c>
+      <c r="C11" s="3" t="n">
+        <v>0.36882</v>
       </c>
       <c r="D11" s="3" t="n">
         <v>0.36882</v>
       </c>
       <c r="E11" s="3" t="n">
-        <v>-0.250553</v>
-      </c>
-      <c r="F11" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="G11" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+        <v>-0.290553</v>
+      </c>
+      <c r="F11" s="3" t="n">
+        <v>-1.302713</v>
+      </c>
+      <c r="G11" s="3" t="n">
+        <v>-1.356318</v>
       </c>
       <c r="H11" s="3" t="n">
-        <v>-0.095982</v>
+        <v>-3.577456</v>
       </c>
       <c r="I11" s="3" t="n">
-        <v>-0.095995</v>
-      </c>
-      <c r="J11" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="K11" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+        <v>-1.640993</v>
+      </c>
+      <c r="J11" s="3" t="n">
+        <v>-1.584424</v>
+      </c>
+      <c r="K11" s="3" t="n">
+        <v>-2.254398</v>
       </c>
       <c r="L11" s="3" t="n">
         <v>-1.427664</v>
@@ -1124,15 +1028,11 @@
           <t xml:space="preserve">    Interest Income</t>
         </is>
       </c>
-      <c r="B12" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="C12" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="B12" s="3" t="n">
+        <v>-0.01139</v>
+      </c>
+      <c r="C12" s="3" t="n">
+        <v>-0.0009840000000000001</v>
       </c>
       <c r="D12" s="3" t="n">
         <v>0</v>
@@ -1140,15 +1040,11 @@
       <c r="E12" s="3" t="n">
         <v>0</v>
       </c>
-      <c r="F12" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="G12" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="F12" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="G12" s="3" t="n">
+        <v>-0.002476</v>
       </c>
       <c r="H12" s="3" t="n">
         <v>-0.013039</v>
@@ -1156,15 +1052,11 @@
       <c r="I12" s="3" t="n">
         <v>-0.010588</v>
       </c>
-      <c r="J12" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="K12" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="J12" s="3" t="n">
+        <v>-0.014768</v>
+      </c>
+      <c r="K12" s="3" t="n">
+        <v>-0.009435000000000001</v>
       </c>
       <c r="L12" s="3" t="n">
         <v>-0.000934</v>
@@ -1194,15 +1086,11 @@
           <t xml:space="preserve">    Interest Expense</t>
         </is>
       </c>
-      <c r="B13" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="C13" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="B13" s="3" t="n">
+        <v>-0</v>
+      </c>
+      <c r="C13" s="3" t="n">
+        <v>-0</v>
       </c>
       <c r="D13" s="3" t="n">
         <v>-0</v>
@@ -1210,15 +1098,11 @@
       <c r="E13" s="3" t="n">
         <v>-0</v>
       </c>
-      <c r="F13" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="G13" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="F13" s="3" t="n">
+        <v>-0</v>
+      </c>
+      <c r="G13" s="3" t="n">
+        <v>-0</v>
       </c>
       <c r="H13" s="3" t="n">
         <v>-0</v>
@@ -1226,15 +1110,11 @@
       <c r="I13" s="3" t="n">
         <v>-0</v>
       </c>
-      <c r="J13" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="K13" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="J13" s="3" t="n">
+        <v>-0</v>
+      </c>
+      <c r="K13" s="3" t="n">
+        <v>-0</v>
       </c>
       <c r="L13" s="3" t="n">
         <v>-0</v>
@@ -1264,15 +1144,11 @@
           <t xml:space="preserve">  Net Interest Income</t>
         </is>
       </c>
-      <c r="B14" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="C14" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="B14" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="C14" s="3" t="n">
+        <v>0</v>
       </c>
       <c r="D14" s="3" t="n">
         <v>0</v>
@@ -1280,15 +1156,11 @@
       <c r="E14" s="3" t="n">
         <v>0</v>
       </c>
-      <c r="F14" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="G14" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="F14" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="G14" s="3" t="n">
+        <v>0</v>
       </c>
       <c r="H14" s="3" t="n">
         <v>0</v>
@@ -1296,15 +1168,11 @@
       <c r="I14" s="3" t="n">
         <v>0</v>
       </c>
-      <c r="J14" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="K14" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="J14" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="K14" s="3" t="n">
+        <v>0</v>
       </c>
       <c r="L14" s="3" t="n">
         <v>0</v>
@@ -1334,15 +1202,11 @@
           <t xml:space="preserve">  Other Income (Expense)</t>
         </is>
       </c>
-      <c r="B15" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="C15" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="B15" s="3" t="n">
+        <v>0.010282</v>
+      </c>
+      <c r="C15" s="3" t="n">
+        <v>0.017221</v>
       </c>
       <c r="D15" s="3" t="n">
         <v>0.009105</v>
@@ -1350,15 +1214,11 @@
       <c r="E15" s="3" t="n">
         <v>0.011245</v>
       </c>
-      <c r="F15" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="G15" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="F15" s="3" t="n">
+        <v>0.000375</v>
+      </c>
+      <c r="G15" s="3" t="n">
+        <v>-0.004386</v>
       </c>
       <c r="H15" s="3" t="n">
         <v>0.035407</v>
@@ -1366,15 +1226,11 @@
       <c r="I15" s="3" t="n">
         <v>0.023545</v>
       </c>
-      <c r="J15" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="K15" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="J15" s="3" t="n">
+        <v>0.032624</v>
+      </c>
+      <c r="K15" s="3" t="n">
+        <v>0.041055</v>
       </c>
       <c r="L15" s="3" t="n">
         <v>-0.007447</v>
@@ -1404,15 +1260,11 @@
           <t>Pretax Income</t>
         </is>
       </c>
-      <c r="B16" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="C16" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="B16" s="3" t="n">
+        <v>-0.958618</v>
+      </c>
+      <c r="C16" s="3" t="n">
+        <v>-0.367836</v>
       </c>
       <c r="D16" s="3" t="n">
         <v>-1.234789</v>
@@ -1420,15 +1272,11 @@
       <c r="E16" s="3" t="n">
         <v>-2.43855</v>
       </c>
-      <c r="F16" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="G16" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="F16" s="3" t="n">
+        <v>-1.302713</v>
+      </c>
+      <c r="G16" s="3" t="n">
+        <v>-1.282686</v>
       </c>
       <c r="H16" s="3" t="n">
         <v>-3.577456</v>
@@ -1436,15 +1284,11 @@
       <c r="I16" s="3" t="n">
         <v>-1.640993</v>
       </c>
-      <c r="J16" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="K16" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="J16" s="3" t="n">
+        <v>-1.082372</v>
+      </c>
+      <c r="K16" s="3" t="n">
+        <v>-2.410008</v>
       </c>
       <c r="L16" s="3" t="n">
         <v>-1.443666</v>
@@ -1456,7 +1300,7 @@
         <v>-2.22793</v>
       </c>
       <c r="O16" s="3" t="n">
-        <v>-0.899548</v>
+        <v>-0.926548</v>
       </c>
       <c r="P16" s="3" t="n">
         <v>-0.576283</v>
@@ -1474,15 +1318,11 @@
           <t xml:space="preserve">  Tax Provision</t>
         </is>
       </c>
-      <c r="B17" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="C17" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="B17" s="3" t="n">
+        <v>-0</v>
+      </c>
+      <c r="C17" s="3" t="n">
+        <v>-0</v>
       </c>
       <c r="D17" s="3" t="n">
         <v>-0</v>
@@ -1490,15 +1330,11 @@
       <c r="E17" s="3" t="n">
         <v>-0</v>
       </c>
-      <c r="F17" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="G17" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="F17" s="3" t="n">
+        <v>-0</v>
+      </c>
+      <c r="G17" s="3" t="n">
+        <v>-0</v>
       </c>
       <c r="H17" s="3" t="n">
         <v>-0</v>
@@ -1506,15 +1342,11 @@
       <c r="I17" s="3" t="n">
         <v>-0</v>
       </c>
-      <c r="J17" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="K17" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="J17" s="3" t="n">
+        <v>-0.179264</v>
+      </c>
+      <c r="K17" s="3" t="n">
+        <v>0.077805</v>
       </c>
       <c r="L17" s="3" t="n">
         <v>0.008000999999999999</v>
@@ -1526,7 +1358,7 @@
         <v>-0</v>
       </c>
       <c r="O17" s="3" t="n">
-        <v>-0</v>
+        <v>0.027</v>
       </c>
       <c r="P17" s="3" t="n">
         <v>-0</v>
@@ -1728,15 +1560,11 @@
           <t xml:space="preserve">    Net Income (Continuing Operations)</t>
         </is>
       </c>
-      <c r="B20" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="C20" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="B20" s="3" t="n">
+        <v>-0.958618</v>
+      </c>
+      <c r="C20" s="3" t="n">
+        <v>-0.367836</v>
       </c>
       <c r="D20" s="3" t="n">
         <v>-1.234789</v>
@@ -1744,15 +1572,11 @@
       <c r="E20" s="3" t="n">
         <v>-2.43855</v>
       </c>
-      <c r="F20" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="G20" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="F20" s="3" t="n">
+        <v>-1.302713</v>
+      </c>
+      <c r="G20" s="3" t="n">
+        <v>-1.282686</v>
       </c>
       <c r="H20" s="3" t="n">
         <v>-3.577456</v>
@@ -1760,15 +1584,11 @@
       <c r="I20" s="3" t="n">
         <v>-1.640993</v>
       </c>
-      <c r="J20" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="K20" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="J20" s="3" t="n">
+        <v>-1.261636</v>
+      </c>
+      <c r="K20" s="3" t="n">
+        <v>-2.332203</v>
       </c>
       <c r="L20" s="3" t="n">
         <v>-1.435665</v>
@@ -1798,15 +1618,11 @@
           <t xml:space="preserve">    Net Income (Discontinued Operations)</t>
         </is>
       </c>
-      <c r="B21" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="C21" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="B21" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="C21" s="3" t="n">
+        <v>0</v>
       </c>
       <c r="D21" s="3" t="n">
         <v>0</v>
@@ -1814,15 +1630,11 @@
       <c r="E21" s="3" t="n">
         <v>0</v>
       </c>
-      <c r="F21" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="G21" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="F21" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="G21" s="3" t="n">
+        <v>0</v>
       </c>
       <c r="H21" s="3" t="n">
         <v>0</v>
@@ -1830,15 +1642,11 @@
       <c r="I21" s="3" t="n">
         <v>0</v>
       </c>
-      <c r="J21" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="K21" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="J21" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="K21" s="3" t="n">
+        <v>0</v>
       </c>
       <c r="L21" s="3" t="n">
         <v>0</v>
@@ -1868,15 +1676,11 @@
           <t xml:space="preserve">  Other Income (Minority Interest)</t>
         </is>
       </c>
-      <c r="B22" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="C22" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="B22" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="C22" s="3" t="n">
+        <v>0</v>
       </c>
       <c r="D22" s="3" t="n">
         <v>0</v>
@@ -1884,15 +1688,11 @@
       <c r="E22" s="3" t="n">
         <v>0</v>
       </c>
-      <c r="F22" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="G22" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="F22" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="G22" s="3" t="n">
+        <v>0</v>
       </c>
       <c r="H22" s="3" t="n">
         <v>0</v>
@@ -1900,15 +1700,11 @@
       <c r="I22" s="3" t="n">
         <v>0</v>
       </c>
-      <c r="J22" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="K22" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="J22" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="K22" s="3" t="n">
+        <v>0</v>
       </c>
       <c r="L22" s="3" t="n">
         <v>0</v>
@@ -1996,15 +1792,11 @@
           <t>EPS (Basic)</t>
         </is>
       </c>
-      <c r="B24" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="C24" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="B24" s="3" t="n">
+        <v>0.03</v>
+      </c>
+      <c r="C24" s="3" t="n">
+        <v>0.01</v>
       </c>
       <c r="D24" s="3" t="n">
         <v>0.03</v>
@@ -2012,15 +1804,11 @@
       <c r="E24" s="3" t="n">
         <v>0.04</v>
       </c>
-      <c r="F24" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="G24" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="F24" s="3" t="n">
+        <v>-0.02</v>
+      </c>
+      <c r="G24" s="3" t="n">
+        <v>-0.02</v>
       </c>
       <c r="H24" s="3" t="n">
         <v>-0.05</v>
@@ -2028,15 +1816,11 @@
       <c r="I24" s="3" t="n">
         <v>-0.02</v>
       </c>
-      <c r="J24" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="K24" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="J24" s="3" t="n">
+        <v>-0.01</v>
+      </c>
+      <c r="K24" s="3" t="n">
+        <v>-0.02</v>
       </c>
       <c r="L24" s="3" t="n">
         <v>-0.01</v>
@@ -2066,15 +1850,11 @@
           <t>EPS (Diluted)</t>
         </is>
       </c>
-      <c r="B25" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="C25" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="B25" s="3" t="n">
+        <v>0.03</v>
+      </c>
+      <c r="C25" s="3" t="n">
+        <v>0.01</v>
       </c>
       <c r="D25" s="3" t="n">
         <v>0.03</v>
@@ -2082,15 +1862,11 @@
       <c r="E25" s="3" t="n">
         <v>0.04</v>
       </c>
-      <c r="F25" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="G25" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="F25" s="3" t="n">
+        <v>-0.02</v>
+      </c>
+      <c r="G25" s="3" t="n">
+        <v>-0.02</v>
       </c>
       <c r="H25" s="3" t="n">
         <v>-0.05</v>
@@ -2098,15 +1874,11 @@
       <c r="I25" s="3" t="n">
         <v>-0.02</v>
       </c>
-      <c r="J25" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="K25" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="J25" s="3" t="n">
+        <v>-0.01</v>
+      </c>
+      <c r="K25" s="3" t="n">
+        <v>-0.02</v>
       </c>
       <c r="L25" s="3" t="n">
         <v>-0.01</v>
@@ -2136,10 +1908,8 @@
           <t>Shares Outstanding (Diluted Average)</t>
         </is>
       </c>
-      <c r="B26" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="B26" s="3" t="n">
+        <v>-31.953933</v>
       </c>
       <c r="C26" s="1" t="inlineStr">
         <is>
@@ -2152,15 +1922,11 @@
       <c r="E26" s="3" t="n">
         <v>-60.96375</v>
       </c>
-      <c r="F26" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="G26" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="F26" s="3" t="n">
+        <v>65.13565</v>
+      </c>
+      <c r="G26" s="3" t="n">
+        <v>64.1343</v>
       </c>
       <c r="H26" s="3" t="n">
         <v>71.54912</v>
@@ -2173,10 +1939,8 @@
           <t>-</t>
         </is>
       </c>
-      <c r="K26" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="K26" s="3" t="n">
+        <v>116.61015</v>
       </c>
       <c r="L26" s="3" t="n">
         <v>103.668851</v>
@@ -2214,15 +1978,11 @@
           <t>EBIT</t>
         </is>
       </c>
-      <c r="B27" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="C27" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="B27" s="3" t="n">
+        <v>-0.947228</v>
+      </c>
+      <c r="C27" s="3" t="n">
+        <v>-0.366852</v>
       </c>
       <c r="D27" s="3" t="n">
         <v>-1.234789</v>
@@ -2230,15 +1990,11 @@
       <c r="E27" s="3" t="n">
         <v>-2.43855</v>
       </c>
-      <c r="F27" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="G27" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="F27" s="3" t="n">
+        <v>-1.302713</v>
+      </c>
+      <c r="G27" s="3" t="n">
+        <v>-1.28021</v>
       </c>
       <c r="H27" s="3" t="n">
         <v>-3.564417</v>
@@ -2246,15 +2002,11 @@
       <c r="I27" s="3" t="n">
         <v>-1.630405</v>
       </c>
-      <c r="J27" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="K27" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="J27" s="3" t="n">
+        <v>-1.067604</v>
+      </c>
+      <c r="K27" s="3" t="n">
+        <v>-2.400573</v>
       </c>
       <c r="L27" s="3" t="n">
         <v>-1.442732</v>
@@ -2266,7 +2018,7 @@
         <v>-2.225463</v>
       </c>
       <c r="O27" s="3" t="n">
-        <v>-0.897864</v>
+        <v>-0.924864</v>
       </c>
       <c r="P27" s="3" t="n">
         <v>-0.576283</v>
@@ -2284,15 +2036,11 @@
           <t xml:space="preserve">  Depreciation, Depletion and Amortization</t>
         </is>
       </c>
-      <c r="B28" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="C28" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="B28" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="C28" s="3" t="n">
+        <v>0</v>
       </c>
       <c r="D28" s="3" t="n">
         <v>0.009969</v>
@@ -2300,15 +2048,11 @@
       <c r="E28" s="3" t="n">
         <v>0.013849</v>
       </c>
-      <c r="F28" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="G28" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="F28" s="3" t="n">
+        <v>0.016499</v>
+      </c>
+      <c r="G28" s="3" t="n">
+        <v>0.011665</v>
       </c>
       <c r="H28" s="3" t="n">
         <v>0.008800000000000001</v>
@@ -2316,15 +2060,11 @@
       <c r="I28" s="3" t="n">
         <v>0.00681</v>
       </c>
-      <c r="J28" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="K28" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="J28" s="3" t="n">
+        <v>0.005544</v>
+      </c>
+      <c r="K28" s="3" t="n">
+        <v>0.0048</v>
       </c>
       <c r="L28" s="3" t="n">
         <v>0.003698</v>
@@ -2354,15 +2094,11 @@
           <t>EBITDA</t>
         </is>
       </c>
-      <c r="B29" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="C29" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="B29" s="3" t="n">
+        <v>-0.947228</v>
+      </c>
+      <c r="C29" s="3" t="n">
+        <v>-0.366852</v>
       </c>
       <c r="D29" s="3" t="n">
         <v>-1.22482</v>
@@ -2370,15 +2106,11 @@
       <c r="E29" s="3" t="n">
         <v>-2.424701</v>
       </c>
-      <c r="F29" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="G29" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="F29" s="3" t="n">
+        <v>-1.286214</v>
+      </c>
+      <c r="G29" s="3" t="n">
+        <v>-1.268545</v>
       </c>
       <c r="H29" s="3" t="n">
         <v>-3.555617</v>
@@ -2386,15 +2118,11 @@
       <c r="I29" s="3" t="n">
         <v>-1.623595</v>
       </c>
-      <c r="J29" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="K29" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="J29" s="3" t="n">
+        <v>-1.06206</v>
+      </c>
+      <c r="K29" s="3" t="n">
+        <v>-2.395773</v>
       </c>
       <c r="L29" s="3" t="n">
         <v>-1.439034</v>
@@ -2406,7 +2134,7 @@
         <v>-2.225463</v>
       </c>
       <c r="O29" s="3" t="n">
-        <v>-0.897864</v>
+        <v>-0.924864</v>
       </c>
       <c r="P29" s="3" t="n">
         <v>-0.5705440000000001</v>
@@ -2516,15 +2244,11 @@
           <t>Tax Rate %</t>
         </is>
       </c>
-      <c r="B31" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="C31" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="B31" s="3" t="n">
+        <v>-0</v>
+      </c>
+      <c r="C31" s="3" t="n">
+        <v>-0</v>
       </c>
       <c r="D31" s="3" t="n">
         <v>-0</v>
@@ -2532,15 +2256,11 @@
       <c r="E31" s="3" t="n">
         <v>-0</v>
       </c>
-      <c r="F31" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="G31" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="F31" s="3" t="n">
+        <v>-0</v>
+      </c>
+      <c r="G31" s="3" t="n">
+        <v>-0</v>
       </c>
       <c r="H31" s="3" t="n">
         <v>-0</v>
@@ -2548,15 +2268,11 @@
       <c r="I31" s="3" t="n">
         <v>-0</v>
       </c>
-      <c r="J31" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="K31" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="J31" s="3" t="n">
+        <v>-16.56214314487071</v>
+      </c>
+      <c r="K31" s="3" t="n">
+        <v>-3.228412519792465</v>
       </c>
       <c r="L31" s="3" t="n">
         <v>-0.5542140633636866</v>
@@ -2568,7 +2284,7 @@
         <v>-0</v>
       </c>
       <c r="O31" s="3" t="n">
-        <v>-0</v>
+        <v>-2.914042229868285</v>
       </c>
       <c r="P31" s="3" t="n">
         <v>-0</v>
@@ -7392,25 +7108,25 @@
         <v>0</v>
       </c>
       <c r="E111" s="3" t="n">
-        <v>0</v>
+        <v>-0.043694</v>
       </c>
       <c r="F111" s="3" t="n">
-        <v>0</v>
+        <v>-0.000549</v>
       </c>
       <c r="G111" s="3" t="n">
-        <v>0</v>
+        <v>-0.002416</v>
       </c>
       <c r="H111" s="3" t="n">
-        <v>0</v>
+        <v>-0.002714</v>
       </c>
       <c r="I111" s="3" t="n">
-        <v>0</v>
+        <v>-0.002844</v>
       </c>
       <c r="J111" s="3" t="n">
-        <v>0</v>
+        <v>-0.002129</v>
       </c>
       <c r="K111" s="3" t="n">
-        <v>0</v>
+        <v>-0.001929</v>
       </c>
       <c r="L111" s="3" t="n">
         <v>0</v>
@@ -7419,7 +7135,7 @@
         <v>0</v>
       </c>
       <c r="N111" s="3" t="n">
-        <v>0</v>
+        <v>-0.002043</v>
       </c>
       <c r="O111" s="3" t="n">
         <v>0</v>
@@ -7578,7 +7294,7 @@
         <v>0</v>
       </c>
       <c r="I114" s="3" t="n">
-        <v>0</v>
+        <v>-0.35</v>
       </c>
       <c r="J114" s="3" t="n">
         <v>0</v>
@@ -7639,16 +7355,16 @@
         <v>0</v>
       </c>
       <c r="J115" s="3" t="n">
-        <v>0</v>
+        <v>0.21348</v>
       </c>
       <c r="K115" s="3" t="n">
         <v>0</v>
       </c>
       <c r="L115" s="3" t="n">
-        <v>0</v>
+        <v>0.94296</v>
       </c>
       <c r="M115" s="3" t="n">
-        <v>0</v>
+        <v>0.055372</v>
       </c>
       <c r="N115" s="3" t="n">
         <v>0</v>
@@ -8804,25 +8520,25 @@
         <v>0</v>
       </c>
       <c r="E134" s="3" t="n">
-        <v>0</v>
+        <v>-0.043694</v>
       </c>
       <c r="F134" s="3" t="n">
-        <v>0</v>
+        <v>-0.000549</v>
       </c>
       <c r="G134" s="3" t="n">
-        <v>0</v>
+        <v>-0.002416</v>
       </c>
       <c r="H134" s="3" t="n">
-        <v>0</v>
+        <v>-0.002714</v>
       </c>
       <c r="I134" s="3" t="n">
-        <v>0</v>
+        <v>-0.002844</v>
       </c>
       <c r="J134" s="3" t="n">
-        <v>0</v>
+        <v>-0.002129</v>
       </c>
       <c r="K134" s="3" t="n">
-        <v>0</v>
+        <v>-0.001929</v>
       </c>
       <c r="L134" s="3" t="n">
         <v>0</v>
@@ -8831,7 +8547,7 @@
         <v>0</v>
       </c>
       <c r="N134" s="3" t="n">
-        <v>0</v>
+        <v>-0.002043</v>
       </c>
       <c r="O134" s="3" t="n">
         <v>0</v>
@@ -8862,10 +8578,10 @@
         <v>-0.693706</v>
       </c>
       <c r="E135" s="3" t="n">
-        <v>-2.181035</v>
+        <v>-2.224729</v>
       </c>
       <c r="F135" s="3" t="n">
-        <v>-1.15821</v>
+        <v>-1.158759</v>
       </c>
       <c r="G135" s="1" t="inlineStr">
         <is>
@@ -8873,13 +8589,13 @@
         </is>
       </c>
       <c r="H135" s="3" t="n">
-        <v>-3.569842</v>
+        <v>-3.572556</v>
       </c>
       <c r="I135" s="3" t="n">
-        <v>-0.9426330000000001</v>
+        <v>-0.945477</v>
       </c>
       <c r="J135" s="3" t="n">
-        <v>-1.564878</v>
+        <v>-1.567007</v>
       </c>
       <c r="K135" s="1" t="inlineStr">
         <is>
@@ -8893,7 +8609,7 @@
         <v>-1.320372</v>
       </c>
       <c r="N135" s="3" t="n">
-        <v>-2.01049</v>
+        <v>-2.012533</v>
       </c>
       <c r="O135" s="1" t="inlineStr">
         <is>
@@ -8925,7 +8641,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:U402"/>
+  <dimension ref="A1:U427"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="16" customWidth="1" min="1" max="1"/>
@@ -29746,7 +29462,11 @@
           <t>Deferred income tax recovery</t>
         </is>
       </c>
-      <c r="D211" t="inlineStr"/>
+      <c r="D211" t="inlineStr">
+        <is>
+          <t>DeferredTax</t>
+        </is>
+      </c>
       <c r="E211" t="inlineStr">
         <is>
           <t>-</t>
@@ -30403,7 +30123,11 @@
           <t>Purchase of equipment</t>
         </is>
       </c>
-      <c r="D218" t="inlineStr"/>
+      <c r="D218" t="inlineStr">
+        <is>
+          <t>PurchaseOfPPE</t>
+        </is>
+      </c>
       <c r="E218" t="inlineStr">
         <is>
           <t>-</t>
@@ -30490,7 +30214,11 @@
           <t>Shares issued for cash</t>
         </is>
       </c>
-      <c r="D219" t="inlineStr"/>
+      <c r="D219" t="inlineStr">
+        <is>
+          <t>CommonStockIssuance</t>
+        </is>
+      </c>
       <c r="E219" t="inlineStr">
         <is>
           <t>-</t>
@@ -31652,7 +31380,11 @@
           <t>Deferred income tax expense</t>
         </is>
       </c>
-      <c r="D231" t="inlineStr"/>
+      <c r="D231" t="inlineStr">
+        <is>
+          <t>DeferredTax</t>
+        </is>
+      </c>
       <c r="E231" t="inlineStr">
         <is>
           <t>-</t>
@@ -31852,7 +31584,11 @@
           <t>Proceeds on sale of marketable securities</t>
         </is>
       </c>
-      <c r="D233" t="inlineStr"/>
+      <c r="D233" t="inlineStr">
+        <is>
+          <t>SaleOfInvestment</t>
+        </is>
+      </c>
       <c r="E233" t="inlineStr">
         <is>
           <t>-</t>
@@ -32941,7 +32677,11 @@
           <t>Deferred income tax expense (recovery)</t>
         </is>
       </c>
-      <c r="D244" t="inlineStr"/>
+      <c r="D244" t="inlineStr">
+        <is>
+          <t>DeferredTax</t>
+        </is>
+      </c>
       <c r="E244" t="inlineStr">
         <is>
           <t>-</t>
@@ -34131,7 +33871,11 @@
           <t>Purchase of marketable securities</t>
         </is>
       </c>
-      <c r="D256" t="inlineStr"/>
+      <c r="D256" t="inlineStr">
+        <is>
+          <t>PurchaseOfInvestment</t>
+        </is>
+      </c>
       <c r="E256" t="inlineStr">
         <is>
           <t>-</t>
@@ -38827,15 +38571,11 @@
           <t>SellingGeneralAndAdministration</t>
         </is>
       </c>
-      <c r="E303" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="F303" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="E303" s="5" t="n">
+        <v>0.023683</v>
+      </c>
+      <c r="F303" s="5" t="n">
+        <v>0.011318</v>
       </c>
       <c r="G303" s="5" t="n">
         <v>0.017756</v>
@@ -38843,15 +38583,11 @@
       <c r="H303" s="5" t="n">
         <v>0.017627</v>
       </c>
-      <c r="I303" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="J303" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="I303" s="5" t="n">
+        <v>0.018304</v>
+      </c>
+      <c r="J303" s="5" t="n">
+        <v>0.012174</v>
       </c>
       <c r="K303" s="5" t="n">
         <v>0.009023</v>
@@ -38859,20 +38595,14 @@
       <c r="L303" s="5" t="n">
         <v>0.013651</v>
       </c>
-      <c r="M303" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="N303" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="O303" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="M303" s="5" t="n">
+        <v>0.041617</v>
+      </c>
+      <c r="N303" s="5" t="n">
+        <v>0.079765</v>
+      </c>
+      <c r="O303" s="5" t="n">
+        <v>0.020171</v>
       </c>
       <c r="P303" t="inlineStr">
         <is>
@@ -38916,15 +38646,11 @@
           <t>OtherOperatingExpenses</t>
         </is>
       </c>
-      <c r="E304" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="F304" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="E304" s="5" t="n">
+        <v>0.014412</v>
+      </c>
+      <c r="F304" s="5" t="n">
+        <v>0.01169</v>
       </c>
       <c r="G304" s="5" t="n">
         <v>0.008487</v>
@@ -38932,15 +38658,11 @@
       <c r="H304" s="5" t="n">
         <v>0.01705</v>
       </c>
-      <c r="I304" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="J304" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="I304" s="5" t="n">
+        <v>0.01909</v>
+      </c>
+      <c r="J304" s="5" t="n">
+        <v>0.013153</v>
       </c>
       <c r="K304" s="5" t="n">
         <v>0.01069</v>
@@ -38948,15 +38670,11 @@
       <c r="L304" s="5" t="n">
         <v>0.007879000000000001</v>
       </c>
-      <c r="M304" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="N304" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="M304" s="5" t="n">
+        <v>0.008017</v>
+      </c>
+      <c r="N304" s="5" t="n">
+        <v>0.0226</v>
       </c>
       <c r="O304" s="5" t="n">
         <v>0.010876</v>
@@ -39304,15 +39022,11 @@
           <t>SellingGeneralAndAdministration</t>
         </is>
       </c>
-      <c r="E308" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="F308" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="E308" s="5" t="n">
+        <v>0.007581</v>
+      </c>
+      <c r="F308" s="5" t="n">
+        <v>0.002905</v>
       </c>
       <c r="G308" s="5" t="n">
         <v>0.015854</v>
@@ -39320,15 +39034,11 @@
       <c r="H308" s="5" t="n">
         <v>0.024954</v>
       </c>
-      <c r="I308" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="J308" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="I308" s="5" t="n">
+        <v>0.019044</v>
+      </c>
+      <c r="J308" s="5" t="n">
+        <v>0.009136</v>
       </c>
       <c r="K308" s="5" t="n">
         <v>0.007347</v>
@@ -39336,15 +39046,11 @@
       <c r="L308" s="5" t="n">
         <v>0.005161</v>
       </c>
-      <c r="M308" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="N308" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="M308" s="5" t="n">
+        <v>0.025474</v>
+      </c>
+      <c r="N308" s="5" t="n">
+        <v>0.023362</v>
       </c>
       <c r="O308" s="5" t="n">
         <v>0.023546</v>
@@ -39389,15 +39095,11 @@
           <t>SellingGeneralAndAdministration</t>
         </is>
       </c>
-      <c r="E309" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="F309" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="E309" s="5" t="n">
+        <v>0.007386</v>
+      </c>
+      <c r="F309" s="5" t="n">
+        <v>0.007173</v>
       </c>
       <c r="G309" s="5" t="n">
         <v>0.009049</v>
@@ -39405,15 +39107,11 @@
       <c r="H309" s="5" t="n">
         <v>0.012022</v>
       </c>
-      <c r="I309" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="J309" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="I309" s="5" t="n">
+        <v>0.009950000000000001</v>
+      </c>
+      <c r="J309" s="5" t="n">
+        <v>0.008545000000000001</v>
       </c>
       <c r="K309" s="5" t="n">
         <v>0.008921999999999999</v>
@@ -39421,15 +39119,11 @@
       <c r="L309" s="5" t="n">
         <v>0.009304</v>
       </c>
-      <c r="M309" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="N309" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="M309" s="5" t="n">
+        <v>0.014969</v>
+      </c>
+      <c r="N309" s="5" t="n">
+        <v>0.008362</v>
       </c>
       <c r="O309" s="5" t="n">
         <v>0.005319</v>
@@ -39599,20 +39293,14 @@
           <t>-</t>
         </is>
       </c>
-      <c r="I311" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="J311" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="K311" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="I311" s="5" t="n">
+        <v>1.302713</v>
+      </c>
+      <c r="J311" s="5" t="n">
+        <v>1.356318</v>
+      </c>
+      <c r="K311" s="5" t="n">
+        <v>3.577456</v>
       </c>
       <c r="L311" t="inlineStr">
         <is>
@@ -40789,15 +40477,11 @@
         </is>
       </c>
       <c r="D323" t="inlineStr"/>
-      <c r="E323" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="F323" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="E323" s="5" t="n">
+        <v>0.047553</v>
+      </c>
+      <c r="F323" s="5" t="n">
+        <v>0.034575</v>
       </c>
       <c r="G323" s="5" t="n">
         <v>0.029588</v>
@@ -40805,15 +40489,11 @@
       <c r="H323" s="5" t="n">
         <v>0.043797</v>
       </c>
-      <c r="I323" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="J323" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="I323" s="5" t="n">
+        <v>0.052098</v>
+      </c>
+      <c r="J323" s="5" t="n">
+        <v>0.033464</v>
       </c>
       <c r="K323" s="5" t="n">
         <v>0.033328</v>
@@ -40821,15 +40501,11 @@
       <c r="L323" s="5" t="n">
         <v>0.031943</v>
       </c>
-      <c r="M323" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="N323" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="M323" s="5" t="n">
+        <v>0.044231</v>
+      </c>
+      <c r="N323" s="5" t="n">
+        <v>0.042516</v>
       </c>
       <c r="O323" s="5" t="n">
         <v>0.051205</v>
@@ -40894,10 +40570,8 @@
       <c r="H324" s="5" t="n">
         <v>0.0144</v>
       </c>
-      <c r="I324" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="I324" s="5" t="n">
+        <v>0.0076</v>
       </c>
       <c r="J324" t="inlineStr">
         <is>
@@ -40914,15 +40588,11 @@
           <t>-</t>
         </is>
       </c>
-      <c r="M324" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="N324" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="M324" s="5" t="n">
+        <v>0.012075</v>
+      </c>
+      <c r="N324" s="5" t="n">
+        <v>0.002484</v>
       </c>
       <c r="O324" s="5" t="n">
         <v>0.000525</v>
@@ -41175,15 +40845,11 @@
           <t>OtherIncomeExpense</t>
         </is>
       </c>
-      <c r="E327" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="F327" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="E327" s="5" t="n">
+        <v>0.010282</v>
+      </c>
+      <c r="F327" s="5" t="n">
+        <v>0.017221</v>
       </c>
       <c r="G327" s="5" t="n">
         <v>0.009105</v>
@@ -41191,10 +40857,8 @@
       <c r="H327" s="5" t="n">
         <v>0.011245</v>
       </c>
-      <c r="I327" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="I327" s="5" t="n">
+        <v>0.000375</v>
       </c>
       <c r="J327" t="inlineStr">
         <is>
@@ -41207,15 +40871,11 @@
       <c r="L327" s="5" t="n">
         <v>0.023545</v>
       </c>
-      <c r="M327" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="N327" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="M327" s="5" t="n">
+        <v>0.032624</v>
+      </c>
+      <c r="N327" s="5" t="n">
+        <v>0.041055</v>
       </c>
       <c r="O327" t="inlineStr">
         <is>
@@ -41466,15 +41126,11 @@
           <t>SellingGeneralAndAdministration</t>
         </is>
       </c>
-      <c r="E330" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="F330" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="E330" s="5" t="n">
+        <v>0.114</v>
+      </c>
+      <c r="F330" s="5" t="n">
+        <v>0.114</v>
       </c>
       <c r="G330" s="5" t="n">
         <v>0.114</v>
@@ -41482,15 +41138,11 @@
       <c r="H330" s="5" t="n">
         <v>0.1645</v>
       </c>
-      <c r="I330" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="J330" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="I330" s="5" t="n">
+        <v>0.0575</v>
+      </c>
+      <c r="J330" s="5" t="n">
+        <v>0.06</v>
       </c>
       <c r="K330" s="5" t="n">
         <v>0.06</v>
@@ -41498,10 +41150,8 @@
       <c r="L330" s="5" t="n">
         <v>0.06</v>
       </c>
-      <c r="M330" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="M330" s="5" t="n">
+        <v>0.15</v>
       </c>
       <c r="N330" t="inlineStr">
         <is>
@@ -41559,15 +41209,11 @@
         </is>
       </c>
       <c r="D331" t="inlineStr"/>
-      <c r="E331" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="F331" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="E331" s="5" t="n">
+        <v>0.069704</v>
+      </c>
+      <c r="F331" s="5" t="n">
+        <v>0.060989</v>
       </c>
       <c r="G331" s="5" t="n">
         <v>0.054254</v>
@@ -41575,10 +41221,8 @@
       <c r="H331" s="5" t="n">
         <v>0.085512</v>
       </c>
-      <c r="I331" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="I331" s="5" t="n">
+        <v>0.097743</v>
       </c>
       <c r="J331" t="inlineStr">
         <is>
@@ -41963,15 +41607,11 @@
           <t>BasicEPS</t>
         </is>
       </c>
-      <c r="E335" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="F335" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="E335" s="5" t="n">
+        <v>3e-08</v>
+      </c>
+      <c r="F335" s="5" t="n">
+        <v>1e-08</v>
       </c>
       <c r="G335" s="5" t="n">
         <v>3e-08</v>
@@ -41979,10 +41619,8 @@
       <c r="H335" s="5" t="n">
         <v>4e-08</v>
       </c>
-      <c r="I335" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="I335" s="5" t="n">
+        <v>2e-08</v>
       </c>
       <c r="J335" t="inlineStr">
         <is>
@@ -42346,7 +41984,11 @@
           <t>Director fees (Note 10)</t>
         </is>
       </c>
-      <c r="D339" t="inlineStr"/>
+      <c r="D339" t="inlineStr">
+        <is>
+          <t>SellingGeneralAndAdministration</t>
+        </is>
+      </c>
       <c r="E339" t="inlineStr">
         <is>
           <t>-</t>
@@ -42458,15 +42100,11 @@
       <c r="H340" s="5" t="n">
         <v>1.18304</v>
       </c>
-      <c r="I340" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="J340" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="I340" s="5" t="n">
+        <v>0.421911</v>
+      </c>
+      <c r="J340" s="5" t="n">
+        <v>0.8231810000000001</v>
       </c>
       <c r="K340" s="5" t="n">
         <v>3.105549</v>
@@ -42474,15 +42112,11 @@
       <c r="L340" s="5" t="n">
         <v>1.114924</v>
       </c>
-      <c r="M340" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="N340" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="M340" s="5" t="n">
+        <v>0.852703</v>
+      </c>
+      <c r="N340" s="5" t="n">
+        <v>1.235421</v>
       </c>
       <c r="O340" s="5" t="n">
         <v>0.805404</v>
@@ -42632,15 +42266,11 @@
           <t>InterestIncomeNonOperating</t>
         </is>
       </c>
-      <c r="E342" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="F342" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="E342" s="5" t="n">
+        <v>-0.01139</v>
+      </c>
+      <c r="F342" s="5" t="n">
+        <v>-0.0009840000000000001</v>
       </c>
       <c r="G342" t="inlineStr">
         <is>
@@ -42668,15 +42298,11 @@
       <c r="L342" s="5" t="n">
         <v>-0.010588</v>
       </c>
-      <c r="M342" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="N342" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="M342" s="5" t="n">
+        <v>-0.014768</v>
+      </c>
+      <c r="N342" s="5" t="n">
+        <v>-0.009435000000000001</v>
       </c>
       <c r="O342" s="5" t="n">
         <v>-0.000934</v>
@@ -42723,15 +42349,11 @@
         </is>
       </c>
       <c r="D343" t="inlineStr"/>
-      <c r="E343" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="F343" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="E343" s="5" t="n">
+        <v>0.069559</v>
+      </c>
+      <c r="F343" s="5" t="n">
+        <v>0.003257</v>
       </c>
       <c r="G343" s="5" t="n">
         <v>0.035386</v>
@@ -42739,31 +42361,23 @@
       <c r="H343" s="5" t="n">
         <v>0.194623</v>
       </c>
-      <c r="I343" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="J343" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="I343" s="5" t="n">
+        <v>0.082556</v>
+      </c>
+      <c r="J343" s="5" t="n">
+        <v>0.032409</v>
       </c>
       <c r="K343" s="5" t="n">
         <v>0.013698</v>
       </c>
       <c r="L343" s="5" t="n">
-        <v>0.003051</v>
-      </c>
-      <c r="M343" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="N343" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+        <v>0.004779</v>
+      </c>
+      <c r="M343" s="5" t="n">
+        <v>0.026059</v>
+      </c>
+      <c r="N343" s="5" t="n">
+        <v>0.030478</v>
       </c>
       <c r="O343" s="5" t="n">
         <v>0.013706</v>
@@ -42929,31 +42543,23 @@
           <t>-</t>
         </is>
       </c>
-      <c r="I345" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="J345" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="I345" s="5" t="n">
+        <v>0.097743</v>
+      </c>
+      <c r="J345" s="5" t="n">
+        <v>0.093362</v>
       </c>
       <c r="K345" s="5" t="n">
         <v>0.07613399999999999</v>
       </c>
       <c r="L345" s="5" t="n">
-        <v>0.06894699999999999</v>
-      </c>
-      <c r="M345" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="N345" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+        <v>0.06947</v>
+      </c>
+      <c r="M345" s="5" t="n">
+        <v>0.077525</v>
+      </c>
+      <c r="N345" s="5" t="n">
+        <v>0.07544099999999999</v>
       </c>
       <c r="O345" s="5" t="n">
         <v>0.07495300000000001</v>
@@ -43296,7 +42902,11 @@
           <t>Deferred income tax recovery (Note 7)</t>
         </is>
       </c>
-      <c r="D349" t="inlineStr"/>
+      <c r="D349" t="inlineStr">
+        <is>
+          <t>TaxProvision</t>
+        </is>
+      </c>
       <c r="E349" t="inlineStr">
         <is>
           <t>-</t>
@@ -43418,10 +43028,8 @@
       <c r="H350" s="5" t="n">
         <v>-2.43855</v>
       </c>
-      <c r="I350" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="I350" s="5" t="n">
+        <v>-1.302713</v>
       </c>
       <c r="J350" t="inlineStr">
         <is>
@@ -43620,20 +43228,14 @@
           <t>-</t>
         </is>
       </c>
-      <c r="I352" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="J352" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="K352" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="I352" s="5" t="n">
+        <v>0.000375</v>
+      </c>
+      <c r="J352" s="5" t="n">
+        <v>-0.004386</v>
+      </c>
+      <c r="K352" s="5" t="n">
+        <v>0.035407</v>
       </c>
       <c r="L352" t="inlineStr">
         <is>
@@ -43905,10 +43507,8 @@
         </is>
       </c>
       <c r="D355" t="inlineStr"/>
-      <c r="E355" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="E355" s="5" t="n">
+        <v>0.01483</v>
       </c>
       <c r="F355" t="inlineStr">
         <is>
@@ -43921,15 +43521,11 @@
       <c r="H355" s="5" t="n">
         <v>0.034186</v>
       </c>
-      <c r="I355" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="J355" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="I355" s="5" t="n">
+        <v>0.024954</v>
+      </c>
+      <c r="J355" s="5" t="n">
+        <v>0.010879</v>
       </c>
       <c r="K355" s="5" t="n">
         <v>0.0047</v>
@@ -43937,15 +43533,11 @@
       <c r="L355" s="5" t="n">
         <v>0.002036</v>
       </c>
-      <c r="M355" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="N355" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="M355" s="5" t="n">
+        <v>0.007791</v>
+      </c>
+      <c r="N355" s="5" t="n">
+        <v>0.010965</v>
       </c>
       <c r="O355" s="5" t="n">
         <v>0.002664</v>
@@ -44439,20 +44031,14 @@
           <t>-</t>
         </is>
       </c>
-      <c r="L360" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="M360" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="N360" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="L360" s="5" t="n">
+        <v>0.021</v>
+      </c>
+      <c r="M360" s="5" t="n">
+        <v>1.322216</v>
+      </c>
+      <c r="N360" s="5" t="n">
+        <v>-0.520695</v>
       </c>
       <c r="O360" s="5" t="n">
         <v>-0.053539</v>
@@ -44911,10 +44497,14 @@
       </c>
       <c r="C365" t="inlineStr">
         <is>
-          <t>Conferences and conventions</t>
-        </is>
-      </c>
-      <c r="D365" t="inlineStr"/>
+          <t>Depreciation (Note 5)</t>
+        </is>
+      </c>
+      <c r="D365" t="inlineStr">
+        <is>
+          <t>Depreciation</t>
+        </is>
+      </c>
       <c r="E365" t="inlineStr">
         <is>
           <t>-</t>
@@ -44925,42 +44515,34 @@
           <t>-</t>
         </is>
       </c>
-      <c r="G365" s="5" t="n">
-        <v>0.031047</v>
+      <c r="G365" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="H365" s="5" t="n">
-        <v>0.041812</v>
-      </c>
-      <c r="I365" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="J365" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+        <v>0.013849</v>
+      </c>
+      <c r="I365" s="5" t="n">
+        <v>0.016499</v>
+      </c>
+      <c r="J365" s="5" t="n">
+        <v>0.011665</v>
       </c>
       <c r="K365" s="5" t="n">
-        <v>0.004332</v>
+        <v>0.008800000000000001</v>
       </c>
       <c r="L365" s="5" t="n">
-        <v>0.001728</v>
-      </c>
-      <c r="M365" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="N365" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="O365" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+        <v>0.00681</v>
+      </c>
+      <c r="M365" s="5" t="n">
+        <v>0.005544</v>
+      </c>
+      <c r="N365" s="5" t="n">
+        <v>0.0048</v>
+      </c>
+      <c r="O365" s="5" t="n">
+        <v>0.003698</v>
       </c>
       <c r="P365" t="inlineStr">
         <is>
@@ -45006,12 +44588,12 @@
       </c>
       <c r="C366" t="inlineStr">
         <is>
-          <t>Depreciation (Note 5)</t>
+          <t>Director fees (Note 9)</t>
         </is>
       </c>
       <c r="D366" t="inlineStr">
         <is>
-          <t>Depreciation</t>
+          <t>SellingGeneralAndAdministration</t>
         </is>
       </c>
       <c r="E366" t="inlineStr">
@@ -45044,26 +44626,26 @@
           <t>-</t>
         </is>
       </c>
-      <c r="K366" s="5" t="n">
-        <v>0.008800000000000001</v>
-      </c>
-      <c r="L366" s="5" t="n">
-        <v>0.00681</v>
+      <c r="K366" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="L366" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="M366" t="inlineStr">
         <is>
           <t>-</t>
         </is>
       </c>
-      <c r="N366" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="O366" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="N366" s="5" t="n">
+        <v>0.048</v>
+      </c>
+      <c r="O366" s="5" t="n">
+        <v>0.042</v>
       </c>
       <c r="P366" t="inlineStr">
         <is>
@@ -45109,10 +44691,14 @@
       </c>
       <c r="C367" t="inlineStr">
         <is>
-          <t>General exploration</t>
-        </is>
-      </c>
-      <c r="D367" t="inlineStr"/>
+          <t>Foreign exchange (gain) loss</t>
+        </is>
+      </c>
+      <c r="D367" t="inlineStr">
+        <is>
+          <t>OtherIncomeExpense</t>
+        </is>
+      </c>
       <c r="E367" t="inlineStr">
         <is>
           <t>-</t>
@@ -45123,11 +44709,15 @@
           <t>-</t>
         </is>
       </c>
-      <c r="G367" s="5" t="n">
-        <v>0.042497</v>
-      </c>
-      <c r="H367" s="5" t="n">
-        <v>0.003245</v>
+      <c r="G367" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="H367" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="I367" t="inlineStr">
         <is>
@@ -45139,26 +44729,26 @@
           <t>-</t>
         </is>
       </c>
-      <c r="K367" s="5" t="n">
-        <v>0.002991</v>
-      </c>
-      <c r="L367" s="5" t="n">
-        <v>0.000523</v>
+      <c r="K367" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="L367" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="M367" t="inlineStr">
         <is>
           <t>-</t>
         </is>
       </c>
-      <c r="N367" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="O367" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="N367" s="5" t="n">
+        <v>0.041055</v>
+      </c>
+      <c r="O367" s="5" t="n">
+        <v>-0.007447</v>
       </c>
       <c r="P367" t="inlineStr">
         <is>
@@ -45204,12 +44794,12 @@
       </c>
       <c r="C368" t="inlineStr">
         <is>
-          <t>Salaries and wages</t>
+          <t>Management fees (Note 9)</t>
         </is>
       </c>
       <c r="D368" t="inlineStr">
         <is>
-          <t>SalariesAndWages</t>
+          <t>SellingGeneralAndAdministration</t>
         </is>
       </c>
       <c r="E368" t="inlineStr">
@@ -45222,11 +44812,15 @@
           <t>-</t>
         </is>
       </c>
-      <c r="G368" s="5" t="n">
-        <v>0.017086</v>
-      </c>
-      <c r="H368" s="5" t="n">
-        <v>0.145659</v>
+      <c r="G368" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="H368" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="I368" t="inlineStr">
         <is>
@@ -45238,26 +44832,24 @@
           <t>-</t>
         </is>
       </c>
-      <c r="K368" s="5" t="n">
-        <v>0.192146</v>
-      </c>
-      <c r="L368" s="5" t="n">
-        <v>0.158444</v>
-      </c>
-      <c r="M368" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="N368" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="O368" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="K368" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="L368" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="M368" s="5" t="n">
+        <v>0.15</v>
+      </c>
+      <c r="N368" s="5" t="n">
+        <v>0.15</v>
+      </c>
+      <c r="O368" s="5" t="n">
+        <v>0.15</v>
       </c>
       <c r="P368" t="inlineStr">
         <is>
@@ -45303,10 +44895,14 @@
       </c>
       <c r="C369" t="inlineStr">
         <is>
-          <t>Share-based compensation (Note 7)</t>
-        </is>
-      </c>
-      <c r="D369" t="inlineStr"/>
+          <t>Salaries and wages (Note 9)</t>
+        </is>
+      </c>
+      <c r="D369" t="inlineStr">
+        <is>
+          <t>SalariesAndWages</t>
+        </is>
+      </c>
       <c r="E369" t="inlineStr">
         <is>
           <t>-</t>
@@ -45317,11 +44913,15 @@
           <t>-</t>
         </is>
       </c>
-      <c r="G369" s="5" t="n">
-        <v>0.341054</v>
-      </c>
-      <c r="H369" s="5" t="n">
-        <v>0.241029</v>
+      <c r="G369" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="H369" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="I369" t="inlineStr">
         <is>
@@ -45333,26 +44933,24 @@
           <t>-</t>
         </is>
       </c>
-      <c r="K369" s="5" t="n">
-        <v>0.017428</v>
-      </c>
-      <c r="L369" s="5" t="n">
-        <v>0.143635</v>
-      </c>
-      <c r="M369" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="N369" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="O369" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="K369" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="L369" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="M369" s="5" t="n">
+        <v>0.235566</v>
+      </c>
+      <c r="N369" s="5" t="n">
+        <v>0.231755</v>
+      </c>
+      <c r="O369" s="5" t="n">
+        <v>0.231978</v>
       </c>
       <c r="P369" t="inlineStr">
         <is>
@@ -45398,14 +44996,10 @@
       </c>
       <c r="C370" t="inlineStr">
         <is>
-          <t>Loss for the year</t>
-        </is>
-      </c>
-      <c r="D370" t="inlineStr">
-        <is>
-          <t>NetIncome</t>
-        </is>
-      </c>
+          <t>Share-based compensation (Note 7)</t>
+        </is>
+      </c>
+      <c r="D370" t="inlineStr"/>
       <c r="E370" t="inlineStr">
         <is>
           <t>-</t>
@@ -45416,20 +45010,14 @@
           <t>-</t>
         </is>
       </c>
-      <c r="G370" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="H370" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="I370" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="G370" s="5" t="n">
+        <v>0.341054</v>
+      </c>
+      <c r="H370" s="5" t="n">
+        <v>0.241029</v>
+      </c>
+      <c r="I370" s="5" t="n">
+        <v>0.225623</v>
       </c>
       <c r="J370" t="inlineStr">
         <is>
@@ -45437,20 +45025,16 @@
         </is>
       </c>
       <c r="K370" s="5" t="n">
-        <v>-3.577456</v>
+        <v>0.017428</v>
       </c>
       <c r="L370" s="5" t="n">
-        <v>-1.640993</v>
-      </c>
-      <c r="M370" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="N370" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+        <v>0.143635</v>
+      </c>
+      <c r="M370" s="5" t="n">
+        <v>0.064997</v>
+      </c>
+      <c r="N370" s="5" t="n">
+        <v>0.256829</v>
       </c>
       <c r="O370" t="inlineStr">
         <is>
@@ -45496,12 +45080,12 @@
       </c>
       <c r="B371" t="inlineStr">
         <is>
-          <t>Unrealized gains on available-for</t>
+          <t>Expenses</t>
         </is>
       </c>
       <c r="C371" t="inlineStr">
         <is>
-          <t>-sale marketable securities (Note 3)</t>
+          <t>Loss for the year before taxes</t>
         </is>
       </c>
       <c r="D371" t="inlineStr"/>
@@ -45541,22 +45125,16 @@
         </is>
       </c>
       <c r="L371" s="5" t="n">
-        <v>0.021</v>
-      </c>
-      <c r="M371" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="N371" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="O371" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+        <v>-1.640993</v>
+      </c>
+      <c r="M371" s="5" t="n">
+        <v>-1.4409</v>
+      </c>
+      <c r="N371" s="5" t="n">
+        <v>-2.254398</v>
+      </c>
+      <c r="O371" s="5" t="n">
+        <v>-1.427664</v>
       </c>
       <c r="P371" t="inlineStr">
         <is>
@@ -45597,17 +45175,17 @@
       </c>
       <c r="B372" t="inlineStr">
         <is>
-          <t>Unrealized gains on available-for</t>
+          <t>Expenses</t>
         </is>
       </c>
       <c r="C372" t="inlineStr">
         <is>
-          <t>Comprehensive loss for the year $</t>
+          <t>Deferred income tax expense (Notes 3 and 12)</t>
         </is>
       </c>
       <c r="D372" t="inlineStr">
         <is>
-          <t>NetIncome</t>
+          <t>TaxProvision</t>
         </is>
       </c>
       <c r="E372" t="inlineStr">
@@ -45640,26 +45218,26 @@
           <t>-</t>
         </is>
       </c>
-      <c r="K372" s="5" t="n">
-        <v>-3.577456</v>
-      </c>
-      <c r="L372" s="5" t="n">
-        <v>-1.619993</v>
+      <c r="K372" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="L372" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="M372" t="inlineStr">
         <is>
           <t>-</t>
         </is>
       </c>
-      <c r="N372" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="O372" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="N372" s="5" t="n">
+        <v>-0.077805</v>
+      </c>
+      <c r="O372" s="5" t="n">
+        <v>-0.008000999999999999</v>
       </c>
       <c r="P372" t="inlineStr">
         <is>
@@ -45700,17 +45278,17 @@
       </c>
       <c r="B373" t="inlineStr">
         <is>
-          <t>Unrealized gains on available-for</t>
+          <t>Expenses</t>
         </is>
       </c>
       <c r="C373" t="inlineStr">
         <is>
-          <t>Loss per share – basic and diluted $</t>
+          <t>Loss for the year</t>
         </is>
       </c>
       <c r="D373" t="inlineStr">
         <is>
-          <t>BasicEPS</t>
+          <t>NetIncome</t>
         </is>
       </c>
       <c r="E373" t="inlineStr">
@@ -45744,25 +45322,19 @@
         </is>
       </c>
       <c r="K373" s="5" t="n">
-        <v>-5e-08</v>
+        <v>-3.577456</v>
       </c>
       <c r="L373" s="5" t="n">
-        <v>-2e-08</v>
-      </c>
-      <c r="M373" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="N373" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="O373" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+        <v>-1.640993</v>
+      </c>
+      <c r="M373" s="5" t="n">
+        <v>-1.261636</v>
+      </c>
+      <c r="N373" s="5" t="n">
+        <v>-2.332203</v>
+      </c>
+      <c r="O373" s="5" t="n">
+        <v>-1.435665</v>
       </c>
       <c r="P373" t="inlineStr">
         <is>
@@ -45803,15 +45375,19 @@
       </c>
       <c r="B374" t="inlineStr">
         <is>
-          <t>Weighted-average number of shares</t>
+          <t>Change in fair value of marketable securities,</t>
         </is>
       </c>
       <c r="C374" t="inlineStr">
         <is>
-          <t>Outstanding – basic and diluted</t>
-        </is>
-      </c>
-      <c r="D374" t="inlineStr"/>
+          <t>Comprehensive loss for the year $</t>
+        </is>
+      </c>
+      <c r="D374" t="inlineStr">
+        <is>
+          <t>NetIncome</t>
+        </is>
+      </c>
       <c r="E374" t="inlineStr">
         <is>
           <t>-</t>
@@ -45842,26 +45418,22 @@
           <t>-</t>
         </is>
       </c>
-      <c r="K374" s="5" t="n">
-        <v>78.74032200000001</v>
+      <c r="K374" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="L374" s="5" t="n">
-        <v>82.67247500000001</v>
-      </c>
-      <c r="M374" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="N374" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="O374" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+        <v>-1.619993</v>
+      </c>
+      <c r="M374" s="5" t="n">
+        <v>-0.082944</v>
+      </c>
+      <c r="N374" s="5" t="n">
+        <v>-2.852898</v>
+      </c>
+      <c r="O374" s="5" t="n">
+        <v>-1.489204</v>
       </c>
       <c r="P374" t="inlineStr">
         <is>
@@ -45902,15 +45474,19 @@
       </c>
       <c r="B375" t="inlineStr">
         <is>
-          <t>Expenses</t>
+          <t>Change in fair value of marketable securities,</t>
         </is>
       </c>
       <c r="C375" t="inlineStr">
         <is>
-          <t>Director fees</t>
-        </is>
-      </c>
-      <c r="D375" t="inlineStr"/>
+          <t>Loss per share – basic and diluted $</t>
+        </is>
+      </c>
+      <c r="D375" t="inlineStr">
+        <is>
+          <t>BasicEPS</t>
+        </is>
+      </c>
       <c r="E375" t="inlineStr">
         <is>
           <t>-</t>
@@ -45921,11 +45497,15 @@
           <t>-</t>
         </is>
       </c>
-      <c r="G375" s="5" t="n">
-        <v>0.04</v>
-      </c>
-      <c r="H375" s="5" t="n">
-        <v>0.04</v>
+      <c r="G375" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="H375" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="I375" t="inlineStr">
         <is>
@@ -45942,25 +45522,17 @@
           <t>-</t>
         </is>
       </c>
-      <c r="L375" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="M375" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="N375" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="O375" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="L375" s="5" t="n">
+        <v>-2e-08</v>
+      </c>
+      <c r="M375" s="5" t="n">
+        <v>-1e-08</v>
+      </c>
+      <c r="N375" s="5" t="n">
+        <v>-2e-08</v>
+      </c>
+      <c r="O375" s="5" t="n">
+        <v>-1e-08</v>
       </c>
       <c r="P375" t="inlineStr">
         <is>
@@ -46001,12 +45573,12 @@
       </c>
       <c r="B376" t="inlineStr">
         <is>
-          <t>Expenses</t>
+          <t>Weighted-average number of shares</t>
         </is>
       </c>
       <c r="C376" t="inlineStr">
         <is>
-          <t>Loan bonus (Note 8)</t>
+          <t>Outstanding – basic and diluted</t>
         </is>
       </c>
       <c r="D376" t="inlineStr"/>
@@ -46026,42 +45598,28 @@
         </is>
       </c>
       <c r="H376" s="5" t="n">
-        <v>0.15</v>
-      </c>
-      <c r="I376" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="J376" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="K376" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="L376" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="M376" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="N376" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="O376" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+        <v>61.645756</v>
+      </c>
+      <c r="I376" s="5" t="n">
+        <v>66.44599599999999</v>
+      </c>
+      <c r="J376" s="5" t="n">
+        <v>73.59422600000001</v>
+      </c>
+      <c r="K376" s="5" t="n">
+        <v>78.74032200000001</v>
+      </c>
+      <c r="L376" s="5" t="n">
+        <v>82.67247500000001</v>
+      </c>
+      <c r="M376" s="5" t="n">
+        <v>95.40895</v>
+      </c>
+      <c r="N376" s="5" t="n">
+        <v>101.897372</v>
+      </c>
+      <c r="O376" s="5" t="n">
+        <v>103.668851</v>
       </c>
       <c r="P376" t="inlineStr">
         <is>
@@ -46107,12 +45665,12 @@
       </c>
       <c r="C377" t="inlineStr">
         <is>
-          <t>Weighted-average number of shares outstanding</t>
+          <t>Total operating expenses</t>
         </is>
       </c>
       <c r="D377" t="inlineStr">
         <is>
-          <t>BasicAverageShares</t>
+          <t>OperatingExpense</t>
         </is>
       </c>
       <c r="E377" t="inlineStr">
@@ -46125,11 +45683,15 @@
           <t>-</t>
         </is>
       </c>
-      <c r="G377" s="5" t="n">
-        <v>46.242948</v>
-      </c>
-      <c r="H377" s="5" t="n">
-        <v>61.645756</v>
+      <c r="G377" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="H377" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="I377" t="inlineStr">
         <is>
@@ -46146,20 +45708,14 @@
           <t>-</t>
         </is>
       </c>
-      <c r="L377" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="M377" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="N377" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="L377" s="5" t="n">
+        <v>1.640993</v>
+      </c>
+      <c r="M377" s="5" t="n">
+        <v>1.584424</v>
+      </c>
+      <c r="N377" s="5" t="n">
+        <v>2.254398</v>
       </c>
       <c r="O377" t="inlineStr">
         <is>
@@ -46205,12 +45761,12 @@
       </c>
       <c r="B378" t="inlineStr">
         <is>
-          <t>Vancouver, British Columbia                                                                  Chartered Accountants</t>
+          <t>Expenses</t>
         </is>
       </c>
       <c r="C378" t="inlineStr">
         <is>
-          <t>March 17,</t>
+          <t>Gain on sale of marketable securities (Note 3)</t>
         </is>
       </c>
       <c r="D378" t="inlineStr"/>
@@ -46224,8 +45780,10 @@
           <t>-</t>
         </is>
       </c>
-      <c r="G378" s="5" t="n">
-        <v>0.002011</v>
+      <c r="G378" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="H378" t="inlineStr">
         <is>
@@ -46252,10 +45810,8 @@
           <t>-</t>
         </is>
       </c>
-      <c r="M378" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="M378" s="5" t="n">
+        <v>0.143524</v>
       </c>
       <c r="N378" t="inlineStr">
         <is>
@@ -46306,15 +45862,19 @@
       </c>
       <c r="B379" t="inlineStr">
         <is>
-          <t>Vancouver, British Columbia                                                                  Chartered Accountants</t>
+          <t>Expenses</t>
         </is>
       </c>
       <c r="C379" t="inlineStr">
         <is>
-          <t>FOR THE YEARS ENDED DECEMBER</t>
-        </is>
-      </c>
-      <c r="D379" t="inlineStr"/>
+          <t>Deferred income tax (expense) recovery (Notes 3 and 12)</t>
+        </is>
+      </c>
+      <c r="D379" t="inlineStr">
+        <is>
+          <t>TaxProvision</t>
+        </is>
+      </c>
       <c r="E379" t="inlineStr">
         <is>
           <t>-</t>
@@ -46325,8 +45885,10 @@
           <t>-</t>
         </is>
       </c>
-      <c r="G379" s="5" t="n">
-        <v>3.1e-05</v>
+      <c r="G379" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="H379" t="inlineStr">
         <is>
@@ -46353,15 +45915,11 @@
           <t>-</t>
         </is>
       </c>
-      <c r="M379" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="N379" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="M379" s="5" t="n">
+        <v>0.179264</v>
+      </c>
+      <c r="N379" s="5" t="n">
+        <v>-0.077805</v>
       </c>
       <c r="O379" t="inlineStr">
         <is>
@@ -46407,12 +45965,12 @@
       </c>
       <c r="B380" t="inlineStr">
         <is>
-          <t>Expenses</t>
+          <t>Other comprehensive income (loss)</t>
         </is>
       </c>
       <c r="C380" t="inlineStr">
         <is>
-          <t>Accounting and audit $ 29,588 $</t>
+          <t>Realized gain on marketable securities (Note 3)</t>
         </is>
       </c>
       <c r="D380" t="inlineStr"/>
@@ -46426,8 +45984,10 @@
           <t>-</t>
         </is>
       </c>
-      <c r="G380" s="5" t="n">
-        <v>0.034575</v>
+      <c r="G380" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="H380" t="inlineStr">
         <is>
@@ -46454,10 +46014,8 @@
           <t>-</t>
         </is>
       </c>
-      <c r="M380" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="M380" s="5" t="n">
+        <v>-0.143524</v>
       </c>
       <c r="N380" t="inlineStr">
         <is>
@@ -46513,12 +46071,12 @@
       </c>
       <c r="C381" t="inlineStr">
         <is>
-          <t>Amortization 9,969</t>
+          <t>Salaries and wages</t>
         </is>
       </c>
       <c r="D381" t="inlineStr">
         <is>
-          <t>Amortization</t>
+          <t>SalariesAndWages</t>
         </is>
       </c>
       <c r="E381" t="inlineStr">
@@ -46532,37 +46090,25 @@
         </is>
       </c>
       <c r="G381" s="5" t="n">
-        <v>0.014578</v>
-      </c>
-      <c r="H381" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="I381" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="J381" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="K381" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="L381" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="M381" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+        <v>0.017086</v>
+      </c>
+      <c r="H381" s="5" t="n">
+        <v>0.145659</v>
+      </c>
+      <c r="I381" s="5" t="n">
+        <v>0.21516</v>
+      </c>
+      <c r="J381" s="5" t="n">
+        <v>0.229607</v>
+      </c>
+      <c r="K381" s="5" t="n">
+        <v>0.192146</v>
+      </c>
+      <c r="L381" s="5" t="n">
+        <v>0.158444</v>
+      </c>
+      <c r="M381" s="5" t="n">
+        <v>0.235566</v>
       </c>
       <c r="N381" t="inlineStr">
         <is>
@@ -46618,10 +46164,14 @@
       </c>
       <c r="C382" t="inlineStr">
         <is>
-          <t>Conferences and conventions 31,047</t>
-        </is>
-      </c>
-      <c r="D382" t="inlineStr"/>
+          <t>Deferred income tax recovery (Notes 3 and 12)</t>
+        </is>
+      </c>
+      <c r="D382" t="inlineStr">
+        <is>
+          <t>TaxProvision</t>
+        </is>
+      </c>
       <c r="E382" t="inlineStr">
         <is>
           <t>-</t>
@@ -46632,8 +46182,10 @@
           <t>-</t>
         </is>
       </c>
-      <c r="G382" s="5" t="n">
-        <v>0.001745</v>
+      <c r="G382" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="H382" t="inlineStr">
         <is>
@@ -46660,10 +46212,8 @@
           <t>-</t>
         </is>
       </c>
-      <c r="M382" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="M382" s="5" t="n">
+        <v>0.179264</v>
       </c>
       <c r="N382" t="inlineStr">
         <is>
@@ -46714,12 +46264,12 @@
       </c>
       <c r="B383" t="inlineStr">
         <is>
-          <t>Expenses</t>
+          <t>Other comprehensive income</t>
         </is>
       </c>
       <c r="C383" t="inlineStr">
         <is>
-          <t>Director fees 40,000</t>
+          <t>Realized gain on marketable securities (Note 3)</t>
         </is>
       </c>
       <c r="D383" t="inlineStr"/>
@@ -46733,8 +46283,10 @@
           <t>-</t>
         </is>
       </c>
-      <c r="G383" s="5" t="n">
-        <v>0.04</v>
+      <c r="G383" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="H383" t="inlineStr">
         <is>
@@ -46761,10 +46313,8 @@
           <t>-</t>
         </is>
       </c>
-      <c r="M383" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="M383" s="5" t="n">
+        <v>-0.143524</v>
       </c>
       <c r="N383" t="inlineStr">
         <is>
@@ -46820,51 +46370,33 @@
       </c>
       <c r="C384" t="inlineStr">
         <is>
-          <t>Foreign exchange loss 9,105</t>
-        </is>
-      </c>
-      <c r="D384" t="inlineStr">
-        <is>
-          <t>OtherIncomeExpense</t>
-        </is>
-      </c>
-      <c r="E384" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="F384" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+          <t>Conferences and conventions</t>
+        </is>
+      </c>
+      <c r="D384" t="inlineStr"/>
+      <c r="E384" s="5" t="n">
+        <v>0.037523</v>
+      </c>
+      <c r="F384" s="5" t="n">
+        <v>0.001745</v>
       </c>
       <c r="G384" s="5" t="n">
-        <v>0.017221</v>
-      </c>
-      <c r="H384" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="I384" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="J384" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="K384" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="L384" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+        <v>0.031047</v>
+      </c>
+      <c r="H384" s="5" t="n">
+        <v>0.041812</v>
+      </c>
+      <c r="I384" s="5" t="n">
+        <v>0.025294</v>
+      </c>
+      <c r="J384" s="5" t="n">
+        <v>0.021749</v>
+      </c>
+      <c r="K384" s="5" t="n">
+        <v>0.004332</v>
+      </c>
+      <c r="L384" s="5" t="n">
+        <v>0.001728</v>
       </c>
       <c r="M384" t="inlineStr">
         <is>
@@ -46925,47 +46457,33 @@
       </c>
       <c r="C385" t="inlineStr">
         <is>
-          <t>General exploration 42,497</t>
+          <t>General exploration</t>
         </is>
       </c>
       <c r="D385" t="inlineStr"/>
-      <c r="E385" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="F385" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="E385" s="5" t="n">
+        <v>0.063196</v>
+      </c>
+      <c r="F385" s="5" t="n">
+        <v>0.040729</v>
       </c>
       <c r="G385" s="5" t="n">
-        <v>0.040729</v>
-      </c>
-      <c r="H385" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="I385" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="J385" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="K385" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="L385" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+        <v>0.042497</v>
+      </c>
+      <c r="H385" s="5" t="n">
+        <v>0.003245</v>
+      </c>
+      <c r="I385" s="5" t="n">
+        <v>0.009011999999999999</v>
+      </c>
+      <c r="J385" s="5" t="n">
+        <v>0.003856</v>
+      </c>
+      <c r="K385" s="5" t="n">
+        <v>0.002991</v>
+      </c>
+      <c r="L385" s="5" t="n">
+        <v>0.000523</v>
       </c>
       <c r="M385" t="inlineStr">
         <is>
@@ -47021,12 +46539,12 @@
       </c>
       <c r="B386" t="inlineStr">
         <is>
-          <t>Expenses</t>
+          <t>Unrealized gains on available-for</t>
         </is>
       </c>
       <c r="C386" t="inlineStr">
         <is>
-          <t>Investor relations and promotions 35,386</t>
+          <t>-sale marketable securities (Note 3)</t>
         </is>
       </c>
       <c r="D386" t="inlineStr"/>
@@ -47040,8 +46558,10 @@
           <t>-</t>
         </is>
       </c>
-      <c r="G386" s="5" t="n">
-        <v>0.003257</v>
+      <c r="G386" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="H386" t="inlineStr">
         <is>
@@ -47063,10 +46583,8 @@
           <t>-</t>
         </is>
       </c>
-      <c r="L386" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="L386" s="5" t="n">
+        <v>0.021</v>
       </c>
       <c r="M386" t="inlineStr">
         <is>
@@ -47122,17 +46640,17 @@
       </c>
       <c r="B387" t="inlineStr">
         <is>
-          <t>Expenses</t>
+          <t>Unrealized gains on available-for</t>
         </is>
       </c>
       <c r="C387" t="inlineStr">
         <is>
-          <t>Legal fees 17,756</t>
+          <t>Comprehensive loss for the year $</t>
         </is>
       </c>
       <c r="D387" t="inlineStr">
         <is>
-          <t>SellingGeneralAndAdministration</t>
+          <t>NetIncome</t>
         </is>
       </c>
       <c r="E387" t="inlineStr">
@@ -47145,8 +46663,10 @@
           <t>-</t>
         </is>
       </c>
-      <c r="G387" s="5" t="n">
-        <v>0.011318</v>
+      <c r="G387" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="H387" t="inlineStr">
         <is>
@@ -47163,15 +46683,11 @@
           <t>-</t>
         </is>
       </c>
-      <c r="K387" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="L387" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="K387" s="5" t="n">
+        <v>-3.577456</v>
+      </c>
+      <c r="L387" s="5" t="n">
+        <v>-1.619993</v>
       </c>
       <c r="M387" t="inlineStr">
         <is>
@@ -47227,17 +46743,17 @@
       </c>
       <c r="B388" t="inlineStr">
         <is>
-          <t>Expenses</t>
+          <t>Unrealized gains on available-for</t>
         </is>
       </c>
       <c r="C388" t="inlineStr">
         <is>
-          <t>Listing and filing fees 8,487</t>
+          <t>Loss per share – basic and diluted $</t>
         </is>
       </c>
       <c r="D388" t="inlineStr">
         <is>
-          <t>OtherOperatingExpenses</t>
+          <t>BasicEPS</t>
         </is>
       </c>
       <c r="E388" t="inlineStr">
@@ -47250,8 +46766,10 @@
           <t>-</t>
         </is>
       </c>
-      <c r="G388" s="5" t="n">
-        <v>0.01169</v>
+      <c r="G388" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="H388" t="inlineStr">
         <is>
@@ -47268,15 +46786,11 @@
           <t>-</t>
         </is>
       </c>
-      <c r="K388" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="L388" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="K388" s="5" t="n">
+        <v>-5e-08</v>
+      </c>
+      <c r="L388" s="5" t="n">
+        <v>-2e-08</v>
       </c>
       <c r="M388" t="inlineStr">
         <is>
@@ -47337,12 +46851,12 @@
       </c>
       <c r="C389" t="inlineStr">
         <is>
-          <t>Management fees 114,000</t>
+          <t>Interest income (Note 3)</t>
         </is>
       </c>
       <c r="D389" t="inlineStr">
         <is>
-          <t>SellingGeneralAndAdministration</t>
+          <t>InterestIncomeNonOperating</t>
         </is>
       </c>
       <c r="E389" t="inlineStr">
@@ -47355,8 +46869,10 @@
           <t>-</t>
         </is>
       </c>
-      <c r="G389" s="5" t="n">
-        <v>0.114</v>
+      <c r="G389" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="H389" t="inlineStr">
         <is>
@@ -47368,15 +46884,11 @@
           <t>-</t>
         </is>
       </c>
-      <c r="J389" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="K389" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="J389" s="5" t="n">
+        <v>-0.002476</v>
+      </c>
+      <c r="K389" s="5" t="n">
+        <v>-0.013039</v>
       </c>
       <c r="L389" t="inlineStr">
         <is>
@@ -47437,12 +46949,12 @@
       </c>
       <c r="B390" t="inlineStr">
         <is>
-          <t>Expenses</t>
+          <t>Other item</t>
         </is>
       </c>
       <c r="C390" t="inlineStr">
         <is>
-          <t>Office services and supplies 71,676</t>
+          <t>Deferred flow-through premium realized (Note 6)</t>
         </is>
       </c>
       <c r="D390" t="inlineStr"/>
@@ -47456,8 +46968,10 @@
           <t>-</t>
         </is>
       </c>
-      <c r="G390" s="5" t="n">
-        <v>0.060989</v>
+      <c r="G390" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="H390" t="inlineStr">
         <is>
@@ -47469,10 +46983,8 @@
           <t>-</t>
         </is>
       </c>
-      <c r="J390" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="J390" s="5" t="n">
+        <v>0.073632</v>
       </c>
       <c r="K390" t="inlineStr">
         <is>
@@ -47538,17 +47050,17 @@
       </c>
       <c r="B391" t="inlineStr">
         <is>
-          <t>Expenses</t>
+          <t>Other item</t>
         </is>
       </c>
       <c r="C391" t="inlineStr">
         <is>
-          <t>Shareholder communications 15,854</t>
+          <t>Loss and comprehensive loss for the year $</t>
         </is>
       </c>
       <c r="D391" t="inlineStr">
         <is>
-          <t>SellingGeneralAndAdministration</t>
+          <t>NetIncome</t>
         </is>
       </c>
       <c r="E391" t="inlineStr">
@@ -47561,28 +47073,24 @@
           <t>-</t>
         </is>
       </c>
-      <c r="G391" s="5" t="n">
-        <v>0.002905</v>
+      <c r="G391" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="H391" t="inlineStr">
         <is>
           <t>-</t>
         </is>
       </c>
-      <c r="I391" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="J391" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="K391" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="I391" s="5" t="n">
+        <v>-1.302713</v>
+      </c>
+      <c r="J391" s="5" t="n">
+        <v>-1.282686</v>
+      </c>
+      <c r="K391" s="5" t="n">
+        <v>-3.577456</v>
       </c>
       <c r="L391" t="inlineStr">
         <is>
@@ -47643,15 +47151,19 @@
       </c>
       <c r="B392" t="inlineStr">
         <is>
-          <t>Expenses</t>
+          <t>Other item</t>
         </is>
       </c>
       <c r="C392" t="inlineStr">
         <is>
-          <t>Stock-based compensation (Note 7) 341,054</t>
-        </is>
-      </c>
-      <c r="D392" t="inlineStr"/>
+          <t>Loss per share – basic and diluted $</t>
+        </is>
+      </c>
+      <c r="D392" t="inlineStr">
+        <is>
+          <t>BasicEPS</t>
+        </is>
+      </c>
       <c r="E392" t="inlineStr">
         <is>
           <t>-</t>
@@ -47662,28 +47174,24 @@
           <t>-</t>
         </is>
       </c>
-      <c r="G392" s="5" t="n">
-        <v>0.00864</v>
+      <c r="G392" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="H392" t="inlineStr">
         <is>
           <t>-</t>
         </is>
       </c>
-      <c r="I392" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="J392" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="K392" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="I392" s="5" t="n">
+        <v>-2e-08</v>
+      </c>
+      <c r="J392" s="5" t="n">
+        <v>-2e-08</v>
+      </c>
+      <c r="K392" s="5" t="n">
+        <v>-5e-08</v>
       </c>
       <c r="L392" t="inlineStr">
         <is>
@@ -47749,7 +47257,7 @@
       </c>
       <c r="C393" t="inlineStr">
         <is>
-          <t>Transfer agent fees 9,049</t>
+          <t>Director fees</t>
         </is>
       </c>
       <c r="D393" t="inlineStr">
@@ -47757,23 +47265,17 @@
           <t>SellingGeneralAndAdministration</t>
         </is>
       </c>
-      <c r="E393" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="F393" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="E393" s="5" t="n">
+        <v>0.04</v>
+      </c>
+      <c r="F393" s="5" t="n">
+        <v>0.04</v>
       </c>
       <c r="G393" s="5" t="n">
-        <v>0.007173</v>
-      </c>
-      <c r="H393" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+        <v>0.04</v>
+      </c>
+      <c r="H393" s="5" t="n">
+        <v>0.04</v>
       </c>
       <c r="I393" t="inlineStr">
         <is>
@@ -47854,7 +47356,7 @@
       </c>
       <c r="C394" t="inlineStr">
         <is>
-          <t>Travel and accommodation 10,541</t>
+          <t>Loan bonus (Note 8)</t>
         </is>
       </c>
       <c r="D394" t="inlineStr"/>
@@ -47873,10 +47375,8 @@
           <t>-</t>
         </is>
       </c>
-      <c r="H394" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="H394" s="5" t="n">
+        <v>0.15</v>
       </c>
       <c r="I394" t="inlineStr">
         <is>
@@ -47957,31 +47457,25 @@
       </c>
       <c r="C395" t="inlineStr">
         <is>
-          <t>Loss before other item 786,009</t>
+          <t>Weighted-average number of shares outstanding</t>
         </is>
       </c>
       <c r="D395" t="inlineStr">
         <is>
-          <t>OperatingIncome</t>
-        </is>
-      </c>
-      <c r="E395" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="F395" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+          <t>BasicAverageShares</t>
+        </is>
+      </c>
+      <c r="E395" s="5" t="n">
+        <v>34.004368</v>
+      </c>
+      <c r="F395" s="5" t="n">
+        <v>36.522455</v>
       </c>
       <c r="G395" s="5" t="n">
-        <v>0.36882</v>
-      </c>
-      <c r="H395" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+        <v>46.242948</v>
+      </c>
+      <c r="H395" s="5" t="n">
+        <v>61.645756</v>
       </c>
       <c r="I395" t="inlineStr">
         <is>
@@ -48057,12 +47551,12 @@
       </c>
       <c r="B396" t="inlineStr">
         <is>
-          <t>Expenses</t>
+          <t>Vancouver, British Columbia                                                                  Chartered Accountants</t>
         </is>
       </c>
       <c r="C396" t="inlineStr">
         <is>
-          <t>Interest income (336)</t>
+          <t>March 17,</t>
         </is>
       </c>
       <c r="D396" t="inlineStr"/>
@@ -48077,7 +47571,7 @@
         </is>
       </c>
       <c r="G396" s="5" t="n">
-        <v>-0.0009840000000000001</v>
+        <v>0.002011</v>
       </c>
       <c r="H396" t="inlineStr">
         <is>
@@ -48158,19 +47652,15 @@
       </c>
       <c r="B397" t="inlineStr">
         <is>
-          <t>Expenses</t>
+          <t>Vancouver, British Columbia                                                                  Chartered Accountants</t>
         </is>
       </c>
       <c r="C397" t="inlineStr">
         <is>
-          <t>Loss and comprehensive loss for the year 785,673</t>
-        </is>
-      </c>
-      <c r="D397" t="inlineStr">
-        <is>
-          <t>NetIncome</t>
-        </is>
-      </c>
+          <t>FOR THE YEARS ENDED DECEMBER</t>
+        </is>
+      </c>
+      <c r="D397" t="inlineStr"/>
       <c r="E397" t="inlineStr">
         <is>
           <t>-</t>
@@ -48182,7 +47672,7 @@
         </is>
       </c>
       <c r="G397" s="5" t="n">
-        <v>-0.367836</v>
+        <v>3.1e-05</v>
       </c>
       <c r="H397" t="inlineStr">
         <is>
@@ -48268,7 +47758,7 @@
       </c>
       <c r="C398" t="inlineStr">
         <is>
-          <t>Deficit - beginning of year 7,070,297</t>
+          <t>Accounting and audit $ 29,588 $</t>
         </is>
       </c>
       <c r="D398" t="inlineStr"/>
@@ -48283,7 +47773,7 @@
         </is>
       </c>
       <c r="G398" s="5" t="n">
-        <v>6.702461</v>
+        <v>0.034575</v>
       </c>
       <c r="H398" t="inlineStr">
         <is>
@@ -48369,10 +47859,14 @@
       </c>
       <c r="C399" t="inlineStr">
         <is>
-          <t>Deficit - end of year $ 7,855,970 $</t>
-        </is>
-      </c>
-      <c r="D399" t="inlineStr"/>
+          <t>Amortization 9,969</t>
+        </is>
+      </c>
+      <c r="D399" t="inlineStr">
+        <is>
+          <t>Amortization</t>
+        </is>
+      </c>
       <c r="E399" t="inlineStr">
         <is>
           <t>-</t>
@@ -48384,7 +47878,7 @@
         </is>
       </c>
       <c r="G399" s="5" t="n">
-        <v>7.070297</v>
+        <v>0.014578</v>
       </c>
       <c r="H399" t="inlineStr">
         <is>
@@ -48470,7 +47964,7 @@
       </c>
       <c r="C400" t="inlineStr">
         <is>
-          <t>Loss per share – basic and diluted $ 0.02 $</t>
+          <t>Conferences and conventions 31,047</t>
         </is>
       </c>
       <c r="D400" t="inlineStr"/>
@@ -48485,7 +47979,7 @@
         </is>
       </c>
       <c r="G400" s="5" t="n">
-        <v>1e-08</v>
+        <v>0.001745</v>
       </c>
       <c r="H400" t="inlineStr">
         <is>
@@ -48571,12 +48065,12 @@
       </c>
       <c r="C401" t="inlineStr">
         <is>
-          <t>Weighted-average number of shares outstanding 46,242,948</t>
+          <t>Director fees 40,000</t>
         </is>
       </c>
       <c r="D401" t="inlineStr">
         <is>
-          <t>BasicAverageShares</t>
+          <t>SellingGeneralAndAdministration</t>
         </is>
       </c>
       <c r="E401" t="inlineStr">
@@ -48590,7 +48084,7 @@
         </is>
       </c>
       <c r="G401" s="5" t="n">
-        <v>36.522455</v>
+        <v>0.04</v>
       </c>
       <c r="H401" t="inlineStr">
         <is>
@@ -48676,91 +48170,2654 @@
       </c>
       <c r="C402" t="inlineStr">
         <is>
+          <t>Foreign exchange loss 9,105</t>
+        </is>
+      </c>
+      <c r="D402" t="inlineStr">
+        <is>
+          <t>OtherIncomeExpense</t>
+        </is>
+      </c>
+      <c r="E402" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="F402" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="G402" s="5" t="n">
+        <v>0.017221</v>
+      </c>
+      <c r="H402" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I402" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="J402" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K402" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="L402" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="M402" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N402" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="O402" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="P402" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="Q402" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="R402" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="S402" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="T402" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="U402" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="403">
+      <c r="A403" t="inlineStr">
+        <is>
+          <t>income_statement</t>
+        </is>
+      </c>
+      <c r="B403" t="inlineStr">
+        <is>
+          <t>Expenses</t>
+        </is>
+      </c>
+      <c r="C403" t="inlineStr">
+        <is>
+          <t>General exploration 42,497</t>
+        </is>
+      </c>
+      <c r="D403" t="inlineStr"/>
+      <c r="E403" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="F403" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="G403" s="5" t="n">
+        <v>0.040729</v>
+      </c>
+      <c r="H403" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I403" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="J403" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K403" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="L403" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="M403" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N403" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="O403" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="P403" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="Q403" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="R403" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="S403" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="T403" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="U403" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="404">
+      <c r="A404" t="inlineStr">
+        <is>
+          <t>income_statement</t>
+        </is>
+      </c>
+      <c r="B404" t="inlineStr">
+        <is>
+          <t>Expenses</t>
+        </is>
+      </c>
+      <c r="C404" t="inlineStr">
+        <is>
+          <t>Investor relations and promotions 35,386</t>
+        </is>
+      </c>
+      <c r="D404" t="inlineStr"/>
+      <c r="E404" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="F404" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="G404" s="5" t="n">
+        <v>0.003257</v>
+      </c>
+      <c r="H404" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I404" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="J404" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K404" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="L404" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="M404" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N404" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="O404" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="P404" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="Q404" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="R404" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="S404" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="T404" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="U404" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="405">
+      <c r="A405" t="inlineStr">
+        <is>
+          <t>income_statement</t>
+        </is>
+      </c>
+      <c r="B405" t="inlineStr">
+        <is>
+          <t>Expenses</t>
+        </is>
+      </c>
+      <c r="C405" t="inlineStr">
+        <is>
+          <t>Legal fees 17,756</t>
+        </is>
+      </c>
+      <c r="D405" t="inlineStr">
+        <is>
+          <t>SellingGeneralAndAdministration</t>
+        </is>
+      </c>
+      <c r="E405" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="F405" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="G405" s="5" t="n">
+        <v>0.011318</v>
+      </c>
+      <c r="H405" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I405" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="J405" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K405" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="L405" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="M405" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N405" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="O405" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="P405" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="Q405" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="R405" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="S405" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="T405" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="U405" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="406">
+      <c r="A406" t="inlineStr">
+        <is>
+          <t>income_statement</t>
+        </is>
+      </c>
+      <c r="B406" t="inlineStr">
+        <is>
+          <t>Expenses</t>
+        </is>
+      </c>
+      <c r="C406" t="inlineStr">
+        <is>
+          <t>Listing and filing fees 8,487</t>
+        </is>
+      </c>
+      <c r="D406" t="inlineStr">
+        <is>
+          <t>OtherOperatingExpenses</t>
+        </is>
+      </c>
+      <c r="E406" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="F406" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="G406" s="5" t="n">
+        <v>0.01169</v>
+      </c>
+      <c r="H406" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I406" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="J406" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K406" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="L406" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="M406" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N406" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="O406" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="P406" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="Q406" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="R406" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="S406" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="T406" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="U406" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="407">
+      <c r="A407" t="inlineStr">
+        <is>
+          <t>income_statement</t>
+        </is>
+      </c>
+      <c r="B407" t="inlineStr">
+        <is>
+          <t>Expenses</t>
+        </is>
+      </c>
+      <c r="C407" t="inlineStr">
+        <is>
+          <t>Management fees 114,000</t>
+        </is>
+      </c>
+      <c r="D407" t="inlineStr">
+        <is>
+          <t>SellingGeneralAndAdministration</t>
+        </is>
+      </c>
+      <c r="E407" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="F407" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="G407" s="5" t="n">
+        <v>0.114</v>
+      </c>
+      <c r="H407" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I407" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="J407" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K407" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="L407" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="M407" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N407" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="O407" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="P407" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="Q407" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="R407" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="S407" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="T407" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="U407" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="408">
+      <c r="A408" t="inlineStr">
+        <is>
+          <t>income_statement</t>
+        </is>
+      </c>
+      <c r="B408" t="inlineStr">
+        <is>
+          <t>Expenses</t>
+        </is>
+      </c>
+      <c r="C408" t="inlineStr">
+        <is>
+          <t>Office services and supplies 71,676</t>
+        </is>
+      </c>
+      <c r="D408" t="inlineStr"/>
+      <c r="E408" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="F408" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="G408" s="5" t="n">
+        <v>0.060989</v>
+      </c>
+      <c r="H408" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I408" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="J408" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K408" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="L408" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="M408" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N408" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="O408" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="P408" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="Q408" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="R408" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="S408" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="T408" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="U408" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="409">
+      <c r="A409" t="inlineStr">
+        <is>
+          <t>income_statement</t>
+        </is>
+      </c>
+      <c r="B409" t="inlineStr">
+        <is>
+          <t>Expenses</t>
+        </is>
+      </c>
+      <c r="C409" t="inlineStr">
+        <is>
+          <t>Shareholder communications 15,854</t>
+        </is>
+      </c>
+      <c r="D409" t="inlineStr">
+        <is>
+          <t>SellingGeneralAndAdministration</t>
+        </is>
+      </c>
+      <c r="E409" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="F409" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="G409" s="5" t="n">
+        <v>0.002905</v>
+      </c>
+      <c r="H409" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I409" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="J409" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K409" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="L409" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="M409" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N409" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="O409" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="P409" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="Q409" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="R409" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="S409" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="T409" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="U409" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="410">
+      <c r="A410" t="inlineStr">
+        <is>
+          <t>income_statement</t>
+        </is>
+      </c>
+      <c r="B410" t="inlineStr">
+        <is>
+          <t>Expenses</t>
+        </is>
+      </c>
+      <c r="C410" t="inlineStr">
+        <is>
+          <t>Stock-based compensation (Note 7) 341,054</t>
+        </is>
+      </c>
+      <c r="D410" t="inlineStr"/>
+      <c r="E410" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="F410" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="G410" s="5" t="n">
+        <v>0.00864</v>
+      </c>
+      <c r="H410" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I410" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="J410" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K410" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="L410" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="M410" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N410" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="O410" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="P410" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="Q410" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="R410" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="S410" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="T410" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="U410" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="411">
+      <c r="A411" t="inlineStr">
+        <is>
+          <t>income_statement</t>
+        </is>
+      </c>
+      <c r="B411" t="inlineStr">
+        <is>
+          <t>Expenses</t>
+        </is>
+      </c>
+      <c r="C411" t="inlineStr">
+        <is>
+          <t>Transfer agent fees 9,049</t>
+        </is>
+      </c>
+      <c r="D411" t="inlineStr">
+        <is>
+          <t>SellingGeneralAndAdministration</t>
+        </is>
+      </c>
+      <c r="E411" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="F411" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="G411" s="5" t="n">
+        <v>0.007173</v>
+      </c>
+      <c r="H411" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I411" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="J411" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K411" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="L411" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="M411" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N411" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="O411" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="P411" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="Q411" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="R411" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="S411" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="T411" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="U411" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="412">
+      <c r="A412" t="inlineStr">
+        <is>
+          <t>income_statement</t>
+        </is>
+      </c>
+      <c r="B412" t="inlineStr">
+        <is>
+          <t>Expenses</t>
+        </is>
+      </c>
+      <c r="C412" t="inlineStr">
+        <is>
+          <t>Travel and accommodation 10,541</t>
+        </is>
+      </c>
+      <c r="D412" t="inlineStr"/>
+      <c r="E412" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="F412" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="G412" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="H412" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I412" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="J412" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K412" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="L412" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="M412" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N412" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="O412" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="P412" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="Q412" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="R412" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="S412" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="T412" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="U412" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="413">
+      <c r="A413" t="inlineStr">
+        <is>
+          <t>income_statement</t>
+        </is>
+      </c>
+      <c r="B413" t="inlineStr">
+        <is>
+          <t>Expenses</t>
+        </is>
+      </c>
+      <c r="C413" t="inlineStr">
+        <is>
+          <t>Loss before other item 786,009</t>
+        </is>
+      </c>
+      <c r="D413" t="inlineStr">
+        <is>
+          <t>OperatingIncome</t>
+        </is>
+      </c>
+      <c r="E413" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="F413" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="G413" s="5" t="n">
+        <v>0.36882</v>
+      </c>
+      <c r="H413" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I413" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="J413" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K413" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="L413" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="M413" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N413" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="O413" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="P413" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="Q413" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="R413" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="S413" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="T413" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="U413" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="414">
+      <c r="A414" t="inlineStr">
+        <is>
+          <t>income_statement</t>
+        </is>
+      </c>
+      <c r="B414" t="inlineStr">
+        <is>
+          <t>Expenses</t>
+        </is>
+      </c>
+      <c r="C414" t="inlineStr">
+        <is>
+          <t>Interest income (336)</t>
+        </is>
+      </c>
+      <c r="D414" t="inlineStr"/>
+      <c r="E414" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="F414" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="G414" s="5" t="n">
+        <v>-0.0009840000000000001</v>
+      </c>
+      <c r="H414" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I414" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="J414" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K414" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="L414" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="M414" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N414" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="O414" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="P414" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="Q414" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="R414" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="S414" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="T414" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="U414" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="415">
+      <c r="A415" t="inlineStr">
+        <is>
+          <t>income_statement</t>
+        </is>
+      </c>
+      <c r="B415" t="inlineStr">
+        <is>
+          <t>Expenses</t>
+        </is>
+      </c>
+      <c r="C415" t="inlineStr">
+        <is>
+          <t>Loss and comprehensive loss for the year 785,673</t>
+        </is>
+      </c>
+      <c r="D415" t="inlineStr">
+        <is>
+          <t>NetIncome</t>
+        </is>
+      </c>
+      <c r="E415" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="F415" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="G415" s="5" t="n">
+        <v>-0.367836</v>
+      </c>
+      <c r="H415" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I415" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="J415" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K415" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="L415" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="M415" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N415" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="O415" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="P415" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="Q415" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="R415" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="S415" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="T415" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="U415" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="416">
+      <c r="A416" t="inlineStr">
+        <is>
+          <t>income_statement</t>
+        </is>
+      </c>
+      <c r="B416" t="inlineStr">
+        <is>
+          <t>Expenses</t>
+        </is>
+      </c>
+      <c r="C416" t="inlineStr">
+        <is>
+          <t>Deficit - beginning of year 7,070,297</t>
+        </is>
+      </c>
+      <c r="D416" t="inlineStr"/>
+      <c r="E416" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="F416" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="G416" s="5" t="n">
+        <v>6.702461</v>
+      </c>
+      <c r="H416" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I416" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="J416" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K416" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="L416" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="M416" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N416" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="O416" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="P416" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="Q416" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="R416" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="S416" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="T416" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="U416" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="417">
+      <c r="A417" t="inlineStr">
+        <is>
+          <t>income_statement</t>
+        </is>
+      </c>
+      <c r="B417" t="inlineStr">
+        <is>
+          <t>Expenses</t>
+        </is>
+      </c>
+      <c r="C417" t="inlineStr">
+        <is>
+          <t>Deficit - end of year $ 7,855,970 $</t>
+        </is>
+      </c>
+      <c r="D417" t="inlineStr"/>
+      <c r="E417" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="F417" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="G417" s="5" t="n">
+        <v>7.070297</v>
+      </c>
+      <c r="H417" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I417" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="J417" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K417" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="L417" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="M417" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N417" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="O417" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="P417" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="Q417" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="R417" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="S417" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="T417" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="U417" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="418">
+      <c r="A418" t="inlineStr">
+        <is>
+          <t>income_statement</t>
+        </is>
+      </c>
+      <c r="B418" t="inlineStr">
+        <is>
+          <t>Expenses</t>
+        </is>
+      </c>
+      <c r="C418" t="inlineStr">
+        <is>
+          <t>Loss per share – basic and diluted $ 0.02 $</t>
+        </is>
+      </c>
+      <c r="D418" t="inlineStr"/>
+      <c r="E418" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="F418" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="G418" s="5" t="n">
+        <v>1e-08</v>
+      </c>
+      <c r="H418" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I418" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="J418" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K418" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="L418" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="M418" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N418" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="O418" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="P418" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="Q418" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="R418" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="S418" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="T418" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="U418" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="419">
+      <c r="A419" t="inlineStr">
+        <is>
+          <t>income_statement</t>
+        </is>
+      </c>
+      <c r="B419" t="inlineStr">
+        <is>
+          <t>Expenses</t>
+        </is>
+      </c>
+      <c r="C419" t="inlineStr">
+        <is>
+          <t>Weighted-average number of shares outstanding 46,242,948</t>
+        </is>
+      </c>
+      <c r="D419" t="inlineStr">
+        <is>
+          <t>BasicAverageShares</t>
+        </is>
+      </c>
+      <c r="E419" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="F419" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="G419" s="5" t="n">
+        <v>36.522455</v>
+      </c>
+      <c r="H419" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I419" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="J419" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K419" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="L419" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="M419" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N419" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="O419" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="P419" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="Q419" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="R419" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="S419" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="T419" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="U419" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="420">
+      <c r="A420" t="inlineStr">
+        <is>
+          <t>income_statement</t>
+        </is>
+      </c>
+      <c r="B420" t="inlineStr">
+        <is>
+          <t>Expenses</t>
+        </is>
+      </c>
+      <c r="C420" t="inlineStr">
+        <is>
           <t>- See Accompanying Notes</t>
         </is>
       </c>
-      <c r="D402" t="inlineStr"/>
-      <c r="E402" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="F402" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="G402" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="H402" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="I402" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="J402" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="K402" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="L402" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="M402" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="N402" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="O402" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="P402" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="Q402" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="R402" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="S402" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="T402" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="U402" t="inlineStr">
+      <c r="D420" t="inlineStr"/>
+      <c r="E420" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="F420" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="G420" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="H420" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I420" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="J420" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K420" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="L420" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="M420" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N420" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="O420" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="P420" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="Q420" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="R420" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="S420" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="T420" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="U420" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="421">
+      <c r="A421" t="inlineStr">
+        <is>
+          <t>income_statement</t>
+        </is>
+      </c>
+      <c r="B421" t="inlineStr">
+        <is>
+          <t>Expenses</t>
+        </is>
+      </c>
+      <c r="C421" t="inlineStr">
+        <is>
+          <t>Amortization</t>
+        </is>
+      </c>
+      <c r="D421" t="inlineStr">
+        <is>
+          <t>Amortization</t>
+        </is>
+      </c>
+      <c r="E421" s="5" t="n">
+        <v>0.019604</v>
+      </c>
+      <c r="F421" s="5" t="n">
+        <v>0.014578</v>
+      </c>
+      <c r="G421" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="H421" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I421" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="J421" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K421" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="L421" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="M421" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N421" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="O421" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="P421" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="Q421" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="R421" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="S421" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="T421" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="U421" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="422">
+      <c r="A422" t="inlineStr">
+        <is>
+          <t>income_statement</t>
+        </is>
+      </c>
+      <c r="B422" t="inlineStr">
+        <is>
+          <t>Expenses</t>
+        </is>
+      </c>
+      <c r="C422" t="inlineStr">
+        <is>
+          <t>Stock-based compensation (Note 7)</t>
+        </is>
+      </c>
+      <c r="D422" t="inlineStr"/>
+      <c r="E422" s="5" t="n">
+        <v>0.180787</v>
+      </c>
+      <c r="F422" s="5" t="n">
+        <v>0.00864</v>
+      </c>
+      <c r="G422" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="H422" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I422" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="J422" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K422" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="L422" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="M422" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N422" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="O422" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="P422" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="Q422" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="R422" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="S422" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="T422" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="U422" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="423">
+      <c r="A423" t="inlineStr">
+        <is>
+          <t>income_statement</t>
+        </is>
+      </c>
+      <c r="B423" t="inlineStr">
+        <is>
+          <t>Expenses</t>
+        </is>
+      </c>
+      <c r="C423" t="inlineStr">
+        <is>
+          <t>Loss before other items</t>
+        </is>
+      </c>
+      <c r="D423" t="inlineStr">
+        <is>
+          <t>OperatingIncome</t>
+        </is>
+      </c>
+      <c r="E423" s="5" t="n">
+        <v>0.7201</v>
+      </c>
+      <c r="F423" s="5" t="n">
+        <v>0.36882</v>
+      </c>
+      <c r="G423" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="H423" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I423" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="J423" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K423" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="L423" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="M423" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N423" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="O423" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="P423" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="Q423" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="R423" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="S423" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="T423" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="U423" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="424">
+      <c r="A424" t="inlineStr">
+        <is>
+          <t>income_statement</t>
+        </is>
+      </c>
+      <c r="B424" t="inlineStr">
+        <is>
+          <t>Expenses</t>
+        </is>
+      </c>
+      <c r="C424" t="inlineStr">
+        <is>
+          <t>Write-down of resource properties (Note 4)</t>
+        </is>
+      </c>
+      <c r="D424" t="inlineStr"/>
+      <c r="E424" s="5" t="n">
+        <v>0.249908</v>
+      </c>
+      <c r="F424" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="G424" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="H424" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I424" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="J424" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K424" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="L424" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="M424" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N424" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="O424" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="P424" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="Q424" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="R424" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="S424" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="T424" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="U424" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="425">
+      <c r="A425" t="inlineStr">
+        <is>
+          <t>income_statement</t>
+        </is>
+      </c>
+      <c r="B425" t="inlineStr">
+        <is>
+          <t>Expenses</t>
+        </is>
+      </c>
+      <c r="C425" t="inlineStr">
+        <is>
+          <t>Loss and comprehensive loss for the year</t>
+        </is>
+      </c>
+      <c r="D425" t="inlineStr">
+        <is>
+          <t>NetIncome</t>
+        </is>
+      </c>
+      <c r="E425" s="5" t="n">
+        <v>-0.958618</v>
+      </c>
+      <c r="F425" s="5" t="n">
+        <v>-0.367836</v>
+      </c>
+      <c r="G425" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="H425" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I425" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="J425" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K425" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="L425" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="M425" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N425" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="O425" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="P425" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="Q425" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="R425" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="S425" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="T425" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="U425" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="426">
+      <c r="A426" t="inlineStr">
+        <is>
+          <t>income_statement</t>
+        </is>
+      </c>
+      <c r="B426" t="inlineStr">
+        <is>
+          <t>Expenses</t>
+        </is>
+      </c>
+      <c r="C426" t="inlineStr">
+        <is>
+          <t>Deficit - beginning of year</t>
+        </is>
+      </c>
+      <c r="D426" t="inlineStr"/>
+      <c r="E426" s="5" t="n">
+        <v>5.743843</v>
+      </c>
+      <c r="F426" s="5" t="n">
+        <v>6.702461</v>
+      </c>
+      <c r="G426" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="H426" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I426" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="J426" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K426" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="L426" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="M426" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N426" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="O426" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="P426" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="Q426" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="R426" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="S426" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="T426" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="U426" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="427">
+      <c r="A427" t="inlineStr">
+        <is>
+          <t>income_statement</t>
+        </is>
+      </c>
+      <c r="B427" t="inlineStr">
+        <is>
+          <t>Expenses</t>
+        </is>
+      </c>
+      <c r="C427" t="inlineStr">
+        <is>
+          <t>Deficit - end of year $</t>
+        </is>
+      </c>
+      <c r="D427" t="inlineStr"/>
+      <c r="E427" s="5" t="n">
+        <v>6.702461</v>
+      </c>
+      <c r="F427" s="5" t="n">
+        <v>7.070297</v>
+      </c>
+      <c r="G427" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="H427" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I427" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="J427" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K427" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="L427" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="M427" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N427" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="O427" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="P427" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="Q427" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="R427" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="S427" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="T427" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="U427" t="inlineStr">
         <is>
           <t>-</t>
         </is>
